--- a/templates/dennis_data_template.xlsx
+++ b/templates/dennis_data_template.xlsx
@@ -329,7 +329,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -438,6 +438,10 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3405,7 +3409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.28515625" bestFit="1" customWidth="1" style="90" min="1" max="1"/>
@@ -4759,6 +4763,45 @@
       <c r="J34" s="7" t="inlineStr">
         <is>
           <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>fiscal_year</t>
+        </is>
+      </c>
+      <c r="B35" s="94" t="inlineStr">
+        <is>
+          <t>Fiscal year (labels the column)</t>
+        </is>
+      </c>
+      <c r="C35" s="95">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Y", IQ_FY - 4)</f>
+        <v/>
+      </c>
+      <c r="D35" s="95">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Y", IQ_FY - 3)</f>
+        <v/>
+      </c>
+      <c r="E35" s="95">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Y", IQ_FY - 2)</f>
+        <v/>
+      </c>
+      <c r="F35" s="95">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Y", IQ_FY - 1)</f>
+        <v/>
+      </c>
+      <c r="G35" s="95">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Y", IQ_FY)</f>
+        <v/>
+      </c>
+      <c r="H35" s="95" t="n"/>
+      <c r="I35" s="96" t="n"/>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>TR.FiscalYear</t>
         </is>
       </c>
     </row>
@@ -4777,7 +4820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="90" min="1" max="1"/>
@@ -5602,35 +5645,35 @@
         </is>
       </c>
       <c r="C20">
-        <f>IF(C18="","",C18-C17)</f>
+        <f>IF(C19="","",C19-C18)</f>
         <v/>
       </c>
       <c r="D20">
-        <f>IF(D18="","",D18-D17)</f>
+        <f>IF(D19="","",D19-D18)</f>
         <v/>
       </c>
       <c r="E20">
-        <f>IF(E18="","",E18-E17)</f>
+        <f>IF(E19="","",E19-E18)</f>
         <v/>
       </c>
       <c r="F20">
-        <f>IF(F18="","",F18-F17)</f>
+        <f>IF(F19="","",F19-F18)</f>
         <v/>
       </c>
       <c r="G20">
-        <f>IF(G18="","",G18-G17)</f>
+        <f>IF(G19="","",G19-G18)</f>
         <v/>
       </c>
       <c r="H20">
-        <f>IF(H18="","",H18-H17)</f>
+        <f>IF(H19="","",H19-H18)</f>
         <v/>
       </c>
       <c r="I20">
-        <f>IF(I18="","",I18-I17)</f>
+        <f>IF(I19="","",I19-I18)</f>
         <v/>
       </c>
       <c r="J20">
-        <f>IF(J18="","",J18-J17)</f>
+        <f>IF(J19="","",J19-J18)</f>
         <v/>
       </c>
       <c r="K20" t="inlineStr">
@@ -5783,6 +5826,251 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="97" t="inlineStr">
+        <is>
+          <t>eps_street</t>
+        </is>
+      </c>
+      <c r="B24" s="97" t="inlineStr">
+        <is>
+          <t>EPS actual (street basis)</t>
+        </is>
+      </c>
+      <c r="C24" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EPS_ACT", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D24" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EPS_ACT", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E24" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EPS_ACT", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F24" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EPS_ACT", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G24" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EPS_ACT", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H24" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EPS_ACT", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I24" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EPS_ACT", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J24" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EPS_ACT", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K24" s="97" t="inlineStr">
+        <is>
+          <t>TR.EPSActValue</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="97" t="inlineStr">
+        <is>
+          <t>eps_consensus</t>
+        </is>
+      </c>
+      <c r="B25" s="97" t="inlineStr">
+        <is>
+          <t>EPS estimate (consensus mean)</t>
+        </is>
+      </c>
+      <c r="C25" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EPS_EST", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D25" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EPS_EST", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E25" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EPS_EST", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F25" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EPS_EST", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G25" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EPS_EST", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H25" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EPS_EST", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I25" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EPS_EST", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J25" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EPS_EST", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K25" s="97" t="inlineStr">
+        <is>
+          <t>TR.EPSMean</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="97" t="inlineStr">
+        <is>
+          <t>revenue_consensus</t>
+        </is>
+      </c>
+      <c r="B26" s="97" t="inlineStr">
+        <is>
+          <t>Revenue estimate (consensus mean)</t>
+        </is>
+      </c>
+      <c r="C26" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_REVENUE_EST", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D26" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_REVENUE_EST", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E26" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_REVENUE_EST", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F26" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_REVENUE_EST", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G26" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_REVENUE_EST", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H26" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_REVENUE_EST", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I26" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_REVENUE_EST", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J26" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_REVENUE_EST", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K26" s="97" t="inlineStr">
+        <is>
+          <t>TR.RevenueMean</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="97" t="inlineStr">
+        <is>
+          <t>fiscal_year</t>
+        </is>
+      </c>
+      <c r="B27" s="97" t="inlineStr">
+        <is>
+          <t>Fiscal year (labels the column)</t>
+        </is>
+      </c>
+      <c r="C27" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Y", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D27" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Y", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E27" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Y", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F27" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Y", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G27" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Y", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H27" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Y", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I27" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Y", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J27" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Y", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K27" s="97" t="inlineStr">
+        <is>
+          <t>TR.FiscalYear</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="97" t="inlineStr">
+        <is>
+          <t>fiscal_quarter</t>
+        </is>
+      </c>
+      <c r="B28" s="97" t="inlineStr">
+        <is>
+          <t>Fiscal quarter (labels the column)</t>
+        </is>
+      </c>
+      <c r="C28" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Q", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D28" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Q", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E28" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Q", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F28" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Q", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G28" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Q", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H28" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Q", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I28" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Q", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J28" s="97">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_FISCAL_Q", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K28" s="97" t="inlineStr">
+        <is>
+          <t>TR.FiscalQuarter</t>
         </is>
       </c>
     </row>

--- a/templates/dennis_data_template.xlsx
+++ b/templates/dennis_data_template.xlsx
@@ -51,15 +51,10 @@
     <definedName name="IQ_WEEK">50000</definedName>
     <definedName name="IQ_YTD">3000</definedName>
     <definedName name="IQ_YTDMONTH" hidden="1">130000</definedName>
-    <definedName name="IQRE51" hidden="1">Snapshot!$D$51:$D$66</definedName>
-    <definedName name="IQRJ51" hidden="1">Snapshot!$I$51:$I$66</definedName>
-    <definedName name="IQRK51" hidden="1">Snapshot!$J$51:$J$4050</definedName>
-    <definedName name="IQRNewsA39" hidden="1">News!$A$40:$A$54</definedName>
     <definedName name="IQRNewsA6" hidden="1">News!$A$7</definedName>
     <definedName name="IQRNewsB6" hidden="1">News!$B$7</definedName>
     <definedName name="IQRNewsC6" hidden="1">News!$C$7</definedName>
     <definedName name="IQRNewsD6" hidden="1">News!$D$7</definedName>
-    <definedName name="IQRP5" hidden="1">Peers!$P$6:$P$15</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -67,7 +62,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00;\(\$#,##0.00\);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;\(\$#,##0\);&quot;-&quot;"/>
@@ -78,6 +73,7 @@
     <numFmt numFmtId="171" formatCode="0.0%"/>
     <numFmt numFmtId="172" formatCode="0.0&quot;x&quot;"/>
     <numFmt numFmtId="173" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="174" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -329,7 +325,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -442,6 +438,10 @@
     <xf numFmtId="166" fontId="7" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="7" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1271,149 +1271,152 @@
     <row r="1" ht="18" customHeight="1" s="90">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>DENNIS — data template v3 (automated)</t>
+          <t>DENNIS — data template v3.2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="36" t="n"/>
+      <c r="A2" s="36" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="37" t="inlineStr">
         <is>
-          <t>What changed: the add-in TR formulas are PRE-FILLED. You just set the ticker.</t>
+          <t>How to fill it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. Set the RIC in Snapshot!B2. Every green cell auto-pulls; grey cells auto-calc.</t>
+          <t xml:space="preserve">  1. Type the ticker into Snapshot!C3 (plain ticker, e.g. BA). Everything else follows it.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Make sure the LSEG/Refinitiv Excel add-in is loaded, then refresh ( / recalc ).</t>
+          <t xml:space="preserve">  2. Excel needs the Capital IQ plug-in signed in. The Peers sheet also uses the LSEG (Refinitiv) add-in;</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Verify the mnemonics in the last column against your entitlement — swap any that error.</t>
+          <t xml:space="preserve">     without it Peers stays empty and the video simply has no peer comparison.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Save as data.xlsx into the video workspace ( workspace/&lt;TICKER&gt;/&lt;date&gt;/ ).</t>
+          <t xml:space="preserve">  3. Refresh (Capital IQ ▸ Refresh Workbook) and wait until no cell says 'Requesting data'.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="n"/>
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Save, and upload the file on the bot's page for that video (it is saved as dennis_data.xlsx).</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
-        <is>
-          <t>Peers auto-pull</t>
-        </is>
-      </c>
+      <c r="A9" s="37" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  The Peers sheet uses =TR("PEERS(&lt;ric&gt;)",...) to fetch Refinitiv's own peer list — no manual RICs.</t>
+          <t>What the bot reads</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Peers is optional and mainly for long-form; skip it for daily shorts.</t>
+          <t xml:space="preserve">  Snapshot, History, Quarters, Valuation, Peers, News and Dashboard, each by name. Don't rename</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="n"/>
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  sheets or the field_key cells in column A/B. Figures are in millions where the column says MM.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="37" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t xml:space="preserve">  The quarter columns are named from Quarters rows 27-29 (fiscal year, fiscal quarter, period end).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cells show #NAME? until the add-in is loaded (the TR function) — that's expected, not a broken file.</t>
+          <t xml:space="preserve">  If all three fail, the bot calls the columns 'the latest quarter', 'the prior quarter' and so on.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  % in POINTS. Currency absolute. Don't rename field_key rows. Bot reads sheets by name, periods dynamically.</t>
-        </is>
-      </c>
+      <c r="A15" s="36" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  On-screen the videos never name the data vendor.</t>
+          <t>Cells left blank on purpose</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A growth rate (CAGR) from or to a loss, ROE on negative equity, a leverage ratio on negative</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>What's new (v3.1 — automation upgrades)</t>
+          <t xml:space="preserve">  EBITDA, P/FCF and EV/FCF on negative cash flow, a reverse-DCF implied growth on negative cash</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  RIC auto-suffix: Snapshot!B3 now derives the Refinitiv RIC from the Capital IQ exchange (D9) via the hidden _RICMap table.</t>
+          <t xml:space="preserve">  flow, and a bear/base/bull price on a loss per share. Each of those numbers means nothing,</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="72" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Set Snapshot!E2 to force a specific RIC. Default suffix .O if the exchange isn't recognised; edit _RICMap to add exchanges.</t>
+          <t xml:space="preserve">  and a writer would read it as a fact.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Peers self-scoring: the Peers sheet now has a percentile block (PERCENTRANK.INC) — this ticker's rank vs peers per metric, with a cheap/expensive &amp; strong/weak read.</t>
-        </is>
-      </c>
+      <c r="A21" s="72" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Valuation: WACC (CAPM, auto) + a reverse DCF (implied growth = WACC − FCF/EV) vs historical CAGR. Bear/base/bull multiples auto-suggest from peer P/E percentiles (override anytime).</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  News sheet: Capital IQ Key Developments (dated headlines) for the ticker — feeds headline-driven shorts. Verify IQ_KEY_DEV_* / IQ_NEWS mnemonics against your entitlement.</t>
+          <t xml:space="preserve">  #NAME? means an add-in is not loaded in this Excel. The bot treats such a cell as missing.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Quarters sheet: the last 8 reported quarters (IQ_FQ − 7 … IQ_FQ). The bot reads QoQ (vs Q-1) and YoY (vs Q-4) from it and prints BOTH — a seasonal Q4 beats its own Q3 every year, so one number alone is misleading. Optional: without it the annual flow is unchanged.</t>
+          <t xml:space="preserve">  On screen the videos never name the data vendor.</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2218,12 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <f>_xll.ciqfunctions.udf.CIQ(C3,"IQ_COMPANY_ADDRESS")</f>
+        <f>TRIM(RIGHT(SUBSTITUTE(_xll.ciqfunctions.udf.CIQ(C3,"IQ_COMPANY_ADDRESS"),",",REPT(" ",200)),200))</f>
         <v/>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>TR.HeadquartersCountry</t>
+          <t>computed: the last part of IQ_COMPANY_ADDRESS (the whole address before)</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -2400,15 +2403,23 @@
       </c>
       <c r="C19" s="43" t="inlineStr">
         <is>
-          <t>Shares Dilluted Outstanding</t>
+          <t>Diluted Shares (latest quarter)</t>
         </is>
       </c>
       <c r="D19" s="16">
-        <f>_xll.ciqfunctions.udf.CIQ(C3, "IQ_SHARESOUTSTANDING_OUT", , D14)</f>
-        <v/>
-      </c>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="8" t="n"/>
+        <f>Quarters!J22</f>
+        <v/>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>computed: Quarters!J22, IQ_DILUT_WEIGHT for the latest quarter (IQ_SHARESOUTSTANDING_OUT was the basic count again)</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n"/>
@@ -2592,9 +2603,10 @@
         <f>_xll.ciqfunctions.udf.CIQ(C3, "IQ_PE_EXCL_FWD_CIQ", IQ_NTM)</f>
         <v/>
       </c>
-      <c r="E26" s="7">
-        <f>_xll.ciqfunctions.udf.CIQ(C3, "IQ_PE_EXCL_FWD_CIQ", IQ_CY)</f>
-        <v/>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>IQ_PE_EXCL_FWD_CIQ</t>
+        </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
@@ -2696,12 +2708,12 @@
         </is>
       </c>
       <c r="D30" s="19">
-        <f>_xlfn.SINGLE(_xll.ciqfunctions.udf.CIQ(C3, "IQ_TEV", , D14)) / (_xlfn.SINGLE(_xll.ciqfunctions.udf.CIQ(C3, "IQ_CASH_OPER", , D14)) + _xlfn.SINGLE(_xll.ciqfunctions.udf.CIQ(C3, "IQ_CAPEX", , D14)))</f>
+        <f>IF(N(History!H15)&gt;0,D17/History!H15,"")</f>
         <v/>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>TR.EVToFCF</t>
+          <t>computed: EV / LTM free cash flow; blank when FCF is not positive</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -2750,12 +2762,12 @@
         </is>
       </c>
       <c r="D32" s="44">
-        <f>_xlfn.SINGLE(_xll.ciqfunctions.udf.CIQ(C3, "IQ_MARKETCAP", , D14)) / (_xlfn.SINGLE(_xll.ciqfunctions.udf.CIQ(C3, "IQ_CASH_OPER", , D14)) + _xlfn.SINGLE(_xll.ciqfunctions.udf.CIQ(C3, "IQ_CAPEX", , D14)))</f>
+        <f>IF(N(History!H15)&gt;0,D16/History!H15,"")</f>
         <v/>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>TR.PriceToFCFPerShare</t>
+          <t>computed: market cap / LTM free cash flow; blank when FCF is not positive</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -2804,12 +2816,12 @@
         </is>
       </c>
       <c r="D34" s="45">
-        <f>1/D25</f>
+        <f>IF(N(D16)&gt;0,IFERROR(History!H11/D16,""),"")</f>
         <v/>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>computed</t>
+          <t>computed: LTM net income / market cap (negative for a loss)</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -2831,12 +2843,12 @@
         </is>
       </c>
       <c r="D35" s="86">
-        <f>_xll.RDP.Data(B3,"TR.FreeOperatingCashFlowExclDividends(Period=LTM,SDate=0D,Curn=USD)/TR.CompanyMarketCap(SDate=0D,Curn=USD)*100/*Free Cash Flow Yield*//*Free Cash Flow Yield*/",,D35)/100</f>
+        <f>IF(N(D16)&gt;0,IFERROR(History!H15/D16,""),"")</f>
         <v/>
       </c>
       <c r="E35" s="80" t="inlineStr">
         <is>
-          <t>computed: LTM FCF / Market Cap (was 1/[P/FCF])</t>
+          <t>computed: LTM free cash flow / market cap (the LSEG RDP.Data call here showed #NAME?)</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -2858,7 +2870,7 @@
         </is>
       </c>
       <c r="D36" s="48">
-        <f>_xll.ciqfunctions.udf.CIQ(C3, "IQ_DIVIDEND_YIELD", D14) /100</f>
+        <f>IFERROR(_xll.ciqfunctions.udf.CIQ(C3, "IQ_DIVIDEND_YIELD", D14)/100,"")</f>
         <v/>
       </c>
       <c r="E36" s="85" t="n"/>
@@ -2881,7 +2893,7 @@
         </is>
       </c>
       <c r="D37" s="48">
-        <f>-_xll.ciqfunctions.udf.CIQ(C3,"IQ_COMMON_REP",IQ_LTM)/D16</f>
+        <f>IFERROR(-_xll.ciqfunctions.udf.CIQ(C3,"IQ_COMMON_REP",IQ_LTM)/D16,"")</f>
         <v/>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -2908,7 +2920,7 @@
         </is>
       </c>
       <c r="D38" s="46">
-        <f>D36+D37</f>
+        <f>IF(AND(NOT(ISNUMBER(D36)),NOT(ISNUMBER(D37))),"",N(D36)+N(D37))</f>
         <v/>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -3020,12 +3032,12 @@
         </is>
       </c>
       <c r="D42" s="19">
-        <f>D41/_xll.ciqfunctions.udf.CIQ(C3, "IQ_EBITDA", IQ_LTM)</f>
+        <f>IF(N(History!H10)&gt;0,D41/History!H10,"")</f>
         <v/>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>TR.NetDebtToEBITDA</t>
+          <t>computed: net debt / LTM EBITDA; blank when EBITDA is not positive</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -3074,7 +3086,7 @@
         </is>
       </c>
       <c r="D44" s="17">
-        <f>_xll.ciqfunctions.udf.CIQ(C3, "IQ_CURRENT_RATIO", IQ_CY)</f>
+        <f>_xll.ciqfunctions.udf.CIQ(C3, "IQ_CURRENT_RATIO", IQ_CQ)</f>
         <v/>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -3101,7 +3113,7 @@
         </is>
       </c>
       <c r="D45" s="17">
-        <f>_xll.ciqfunctions.udf.CIQ(C3, "IQ_QUICK_RATIO", IQ_CY)</f>
+        <f>_xll.ciqfunctions.udf.CIQ(C3, "IQ_QUICK_RATIO", IQ_CQ)</f>
         <v/>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -3280,7 +3292,7 @@
         </is>
       </c>
       <c r="D50" s="49">
-        <f>IF(N($L$50)=0,"",IF($D$18=0,"",IF(OR(IF($L$50&lt;=100,$L$50/100,$L$50/$D$18)&lt;0,IF($L$50&lt;=100,$L$50/100,$L$50/$D$18)&gt;1),"",IF($L$50&lt;=100,$L$50/100,$L$50/$D$18))))</f>
+        <f>IF(N($L$50)=0,"",IF(N($D$18)=0,"",IF(OR(IF($L$50&lt;=100,$L$50/100,IF($L$50&lt;=$D$18,$L$50/$D$18,$L$50/($D$18*1000000)))&lt;0,IF($L$50&lt;=100,$L$50/100,IF($L$50&lt;=$D$18,$L$50/$D$18,$L$50/($D$18*1000000)))&gt;1),"",IF($L$50&lt;=100,$L$50/100,IF($L$50&lt;=$D$18,$L$50/$D$18,$L$50/($D$18*1000000))))))</f>
         <v/>
       </c>
       <c r="E50" s="7" t="inlineStr">
@@ -3340,7 +3352,7 @@
         </is>
       </c>
       <c r="D51" s="49">
-        <f>IF(N($L$51)=0,"",IF($D$18=0,"",IF(OR(IF($L$51&lt;=100,$L$51/100,$L$51/$D$18)&lt;0,IF($L$51&lt;=100,$L$51/100,$L$51/$D$18)&gt;1),"",IF($L$51&lt;=100,$L$51/100,$L$51/$D$18))))</f>
+        <f>IF(N($L$51)=0,"",IF(N($D$18)=0,"",IF(OR(IF($L$51&lt;=100,$L$51/100,IF($L$51&lt;=$D$18,$L$51/$D$18,$L$51/($D$18*1000000)))&lt;0,IF($L$51&lt;=100,$L$51/100,IF($L$51&lt;=$D$18,$L$51/$D$18,$L$51/($D$18*1000000)))&gt;1),"",IF($L$51&lt;=100,$L$51/100,IF($L$51&lt;=$D$18,$L$51/$D$18,$L$51/($D$18*1000000))))))</f>
         <v/>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -3390,7 +3402,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>insider_own (D50) and institutional_own (D51) are COMPUTED, not read from a vendor percentage field. TR.InsiderPercentHeld / TR.InstitutionsPercentHeld do not resolve on this licence, and the add-in reports that as the TEXT 'The formula must contain at least one field or function' rather than as an Excel error — which is why an IFERROR chain silently stops at the first bad name instead of trying the next. The resolver at G47:M51 uses ISNUMBER instead: four candidate field names per row, first numeric one wins, M50/M51 name it. D50/D51 then normalise — a figure &lt;=100 is a percent so it is divided by 100, anything larger is a share count so it is divided by shares outstanding (D18) — and blank anything outside 0-1. IF M SAYS 'none resolved': open Formula Builder, find the insider / institutional field your licence exposes, paste its name into H50 or H51, and everything downstream works unchanged.</t>
+          <t>insider_own (D50) and institutional_own (D51) are COMPUTED, not read from a vendor percentage field. The add-ins report a field they do not know as TEXT ('(Invalid Formula Name)', or 'The formula must contain at least one field or function'), not as an Excel error, so an IFERROR chain stops at the first bad name. The resolver at G47:M51 uses ISNUMBER instead: four candidate field names per row, first numeric one wins, M50/M51 name it. D50/D51 then normalise: a figure up to 100 is a percent; up to the share count in D18 (millions) it is millions of shares; above that it is a plain share count (IQ_INSIDER_SHARES returns one, 38,347,842 for GME). Anything outside 0-1 is blanked. IF M SAYS 'none resolved': open Formula Builder, find the field your licence exposes, paste its name into H50 or H51.</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.28515625" bestFit="1" customWidth="1" style="90" min="1" max="1"/>
@@ -3429,7 +3441,7 @@
     <row r="2">
       <c r="A2" s="89" t="inlineStr">
         <is>
-          <t>Green rows auto-pull per period; grey rows/CAGR auto-calc. Set the RIC on Snapshot; refresh.</t>
+          <t>Green rows auto-pull per period; grey rows/CAGR auto-calc. Set the ticker on Snapshot!C3; refresh. A CAGR, a ratio over negative equity or EBITDA, and a multiple of negative cash are left blank: they mean nothing.</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3533,7 @@
         <v/>
       </c>
       <c r="I5" s="18">
-        <f>IFERROR(((G5/C5)^(1/4)-1)*100,"")</f>
+        <f>IF(AND(N(C5)&gt;0,N(G5)&gt;0),((G5/C5)^(1/4)-1)*100,"")</f>
         <v/>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -3566,7 +3578,7 @@
         <v/>
       </c>
       <c r="I6" s="18">
-        <f>IFERROR(((G6/C6)^(1/4)-1)*100,"")</f>
+        <f>IF(AND(N(C6)&gt;0,N(G6)&gt;0),((G6/C6)^(1/4)-1)*100,"")</f>
         <v/>
       </c>
       <c r="J6" s="7" t="inlineStr">
@@ -3653,7 +3665,7 @@
         <v/>
       </c>
       <c r="I8" s="18">
-        <f>IFERROR(((G8/C8)^(1/4)-1)*100,"")</f>
+        <f>IF(AND(N(C8)&gt;0,N(G8)&gt;0),((G8/C8)^(1/4)-1)*100,"")</f>
         <v/>
       </c>
       <c r="J8" s="7" t="inlineStr">
@@ -3740,7 +3752,7 @@
         <v/>
       </c>
       <c r="I10" s="18">
-        <f>IFERROR(((G10/C10)^(1/4)-1)*100,"")</f>
+        <f>IF(AND(N(C10)&gt;0,N(G10)&gt;0),((G10/C10)^(1/4)-1)*100,"")</f>
         <v/>
       </c>
       <c r="J10" s="7" t="inlineStr">
@@ -3785,7 +3797,7 @@
         <v/>
       </c>
       <c r="I11" s="18">
-        <f>IFERROR(((G11/C11)^(1/4)-1)*100,"")</f>
+        <f>IF(AND(N(C11)&gt;0,N(G11)&gt;0),((G11/C11)^(1/4)-1)*100,"")</f>
         <v/>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -3872,7 +3884,7 @@
         <v/>
       </c>
       <c r="I13" s="18">
-        <f>IFERROR(((G13/C13)^(1/4)-1)*100,"")</f>
+        <f>IF(AND(N(C13)&gt;0,N(G13)&gt;0),((G13/C13)^(1/4)-1)*100,"")</f>
         <v/>
       </c>
       <c r="J13" s="7" t="inlineStr">
@@ -3959,7 +3971,7 @@
         <v/>
       </c>
       <c r="I15" s="18">
-        <f>IFERROR(((G15/C15)^(1/4)-1)*100,"")</f>
+        <f>IF(AND(N(C15)&gt;0,N(G15)&gt;0),((G15/C15)^(1/4)-1)*100,"")</f>
         <v/>
       </c>
       <c r="J15" s="7" t="inlineStr">
@@ -4186,7 +4198,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Cash &amp; Equivalents</t>
+          <t>Cash &amp; ST Investments</t>
         </is>
       </c>
       <c r="C21" s="15">
@@ -4442,27 +4454,27 @@
         </is>
       </c>
       <c r="C27" s="22">
-        <f>IFERROR(C23/C10*1,"")</f>
+        <f>IF(N(C10)&gt;0,C23/C10,"")</f>
         <v/>
       </c>
       <c r="D27" s="22">
-        <f>IFERROR(D23/D10*1,"")</f>
+        <f>IF(N(D10)&gt;0,D23/D10,"")</f>
         <v/>
       </c>
       <c r="E27" s="22">
-        <f>IFERROR(E23/E10*1,"")</f>
+        <f>IF(N(E10)&gt;0,E23/E10,"")</f>
         <v/>
       </c>
       <c r="F27" s="22">
-        <f>IFERROR(F23/F10*1,"")</f>
+        <f>IF(N(F10)&gt;0,F23/F10,"")</f>
         <v/>
       </c>
       <c r="G27" s="22">
-        <f>IFERROR(G23/G10*1,"")</f>
+        <f>IF(N(G10)&gt;0,G23/G10,"")</f>
         <v/>
       </c>
       <c r="H27" s="22">
-        <f>IFERROR(H23/H10*1,"")</f>
+        <f>IF(N(H10)&gt;0,H23/H10,"")</f>
         <v/>
       </c>
       <c r="I27" s="5" t="n"/>
@@ -4610,27 +4622,27 @@
         </is>
       </c>
       <c r="C31" s="18">
-        <f>IFERROR(C8*(1-Valuation!$B$22)/C26*100,"")</f>
+        <f>IF(N(C26)&gt;0,C8*(1-Valuation!$B$22)/C26*100,"")</f>
         <v/>
       </c>
       <c r="D31" s="18">
-        <f>IFERROR(D8*(1-Valuation!$B$22)/D26*100,"")</f>
+        <f>IF(N(D26)&gt;0,D8*(1-Valuation!$B$22)/D26*100,"")</f>
         <v/>
       </c>
       <c r="E31" s="18">
-        <f>IFERROR(E8*(1-Valuation!$B$22)/E26*100,"")</f>
+        <f>IF(N(E26)&gt;0,E8*(1-Valuation!$B$22)/E26*100,"")</f>
         <v/>
       </c>
       <c r="F31" s="18">
-        <f>IFERROR(F8*(1-Valuation!$B$22)/F26*100,"")</f>
+        <f>IF(N(F26)&gt;0,F8*(1-Valuation!$B$22)/F26*100,"")</f>
         <v/>
       </c>
       <c r="G31" s="18">
-        <f>IFERROR(G8*(1-Valuation!$B$22)/G26*100,"")</f>
+        <f>IF(N(G26)&gt;0,G8*(1-Valuation!$B$22)/G26*100,"")</f>
         <v/>
       </c>
       <c r="H31" s="18">
-        <f>IFERROR(H8*(1-Valuation!$B$22)/H26*100,"")</f>
+        <f>IF(N(H26)&gt;0,H8*(1-Valuation!$B$22)/H26*100,"")</f>
         <v/>
       </c>
       <c r="I31" s="5" t="n"/>
@@ -4652,27 +4664,27 @@
         </is>
       </c>
       <c r="C32" s="18">
-        <f>IFERROR(C11/C24*100,"")</f>
+        <f>IF(N(C24)&gt;0,C11/C24*100,"")</f>
         <v/>
       </c>
       <c r="D32" s="18">
-        <f>IFERROR(D11/D24*100,"")</f>
+        <f>IF(N(D24)&gt;0,D11/D24*100,"")</f>
         <v/>
       </c>
       <c r="E32" s="18">
-        <f>IFERROR(E11/E24*100,"")</f>
+        <f>IF(N(E24)&gt;0,E11/E24*100,"")</f>
         <v/>
       </c>
       <c r="F32" s="18">
-        <f>IFERROR(F11/F24*100,"")</f>
+        <f>IF(N(F24)&gt;0,F11/F24*100,"")</f>
         <v/>
       </c>
       <c r="G32" s="18">
-        <f>IFERROR(G11/G24*100,"")</f>
+        <f>IF(N(G24)&gt;0,G11/G24*100,"")</f>
         <v/>
       </c>
       <c r="H32" s="18">
-        <f>IFERROR(H11/H24*100,"")</f>
+        <f>IF(N(H24)&gt;0,H11/H24*100,"")</f>
         <v/>
       </c>
       <c r="I32" s="5" t="n"/>
@@ -4718,7 +4730,7 @@
         <v/>
       </c>
       <c r="I33" s="18">
-        <f>IFERROR(((G33/C33)^(1/4)-1)*100,"")</f>
+        <f>IF(AND(N(C33)&gt;0,N(G33)&gt;0),((G33/C33)^(1/4)-1)*100,"")</f>
         <v/>
       </c>
       <c r="J33" s="7" t="inlineStr">
@@ -4802,6 +4814,45 @@
       <c r="J35" s="7" t="inlineStr">
         <is>
           <t>TR.FiscalYear</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>period_end</t>
+        </is>
+      </c>
+      <c r="B36" s="94" t="inlineStr">
+        <is>
+          <t>Fiscal year end date (names a year the row above does not)</t>
+        </is>
+      </c>
+      <c r="C36" s="99">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_PERIODDATE", IQ_FY - 4)</f>
+        <v/>
+      </c>
+      <c r="D36" s="99">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_PERIODDATE", IQ_FY - 3)</f>
+        <v/>
+      </c>
+      <c r="E36" s="99">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_PERIODDATE", IQ_FY - 2)</f>
+        <v/>
+      </c>
+      <c r="F36" s="99">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_PERIODDATE", IQ_FY - 1)</f>
+        <v/>
+      </c>
+      <c r="G36" s="99">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_PERIODDATE", IQ_FY)</f>
+        <v/>
+      </c>
+      <c r="H36" s="100" t="n"/>
+      <c r="I36" s="101" t="n"/>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>IQ_PERIODDATE</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="90" min="1" max="1"/>
@@ -4837,7 +4888,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Green rows auto-pull per quarter; grey rows auto-calc. Q-0 is the latest reported quarter. Read QoQ (Q-1) and YoY (Q-4) together — a retailer beats its own Q3 every December.</t>
+          <t>Green rows auto-pull per quarter; grey rows auto-calc. Q-0 is the latest reported quarter. Read QoQ (Q-1) and YoY (Q-4) together: a retailer beats its own Q3 every December. Rows 27-29 NAME the columns (Q3 FY26): the bot needs the fiscal year at least, or the period end date.</t>
         </is>
       </c>
     </row>
@@ -6071,6 +6122,55 @@
       <c r="K28" s="97" t="inlineStr">
         <is>
           <t>TR.FiscalQuarter</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="97" t="inlineStr">
+        <is>
+          <t>period_end</t>
+        </is>
+      </c>
+      <c r="B29" s="97" t="inlineStr">
+        <is>
+          <t>Period end date (names a quarter no fiscal row names)</t>
+        </is>
+      </c>
+      <c r="C29" s="98">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_PERIODDATE", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D29" s="98">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_PERIODDATE", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E29" s="98">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_PERIODDATE", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F29" s="98">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_PERIODDATE", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G29" s="98">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_PERIODDATE", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H29" s="98">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_PERIODDATE", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I29" s="98">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_PERIODDATE", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J29" s="98">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_PERIODDATE", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K29" s="97" t="inlineStr">
+        <is>
+          <t>IQ_PERIODDATE</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6205,7 @@
     <row r="2">
       <c r="A2" s="92" t="inlineStr">
         <is>
-          <t>Bear/base/bull exit multiples now AUTO-SUGGEST from peer P/E percentiles (yellow — override anytime). WACC + reverse DCF below are fully auto.</t>
+          <t>Bear/base/bull exit multiples AUTO-SUGGEST from peer P/E percentiles (yellow, override anytime). WACC + reverse DCF below are fully auto. A loss per share has no bear/base/bull price, and negative free cash flow has no implied growth: those cells stay blank.</t>
         </is>
       </c>
     </row>
@@ -6206,11 +6306,11 @@
         <v/>
       </c>
       <c r="E10" s="29">
-        <f>IFERROR(B10*D10,"")</f>
+        <f>IF(AND(ISNUMBER(B10),N(B10)&gt;0,ISNUMBER(D10)),B10*D10,"")</f>
         <v/>
       </c>
       <c r="F10" s="30">
-        <f>IFERROR((E10/$B$5-1)*100,"")</f>
+        <f>IF(ISNUMBER(E10),(E10/$B$5-1)*100,"")</f>
         <v/>
       </c>
     </row>
@@ -6234,11 +6334,11 @@
         <v/>
       </c>
       <c r="E11" s="29">
-        <f>IFERROR(B11*D11,"")</f>
+        <f>IF(AND(ISNUMBER(B11),N(B11)&gt;0,ISNUMBER(D11)),B11*D11,"")</f>
         <v/>
       </c>
       <c r="F11" s="30">
-        <f>IFERROR((E11/$B$5-1)*100,"")</f>
+        <f>IF(ISNUMBER(E11),(E11/$B$5-1)*100,"")</f>
         <v/>
       </c>
     </row>
@@ -6262,11 +6362,11 @@
         <v/>
       </c>
       <c r="E12" s="29">
-        <f>IFERROR(B12*D12,"")</f>
+        <f>IF(AND(ISNUMBER(B12),N(B12)&gt;0,ISNUMBER(D12)),B12*D12,"")</f>
         <v/>
       </c>
       <c r="F12" s="30">
-        <f>IFERROR((E12/$B$5-1)*100,"")</f>
+        <f>IF(ISNUMBER(E12),(E12/$B$5-1)*100,"")</f>
         <v/>
       </c>
     </row>
@@ -6459,7 +6559,7 @@
         </is>
       </c>
       <c r="B33" s="66">
-        <f>IFERROR(B32/B31,"")</f>
+        <f>IF(N(B31)&gt;0,IFERROR(B32/B31,""),"")</f>
         <v/>
       </c>
     </row>
@@ -6470,7 +6570,7 @@
         </is>
       </c>
       <c r="B34" s="69">
-        <f>IFERROR(B28-B33,"")</f>
+        <f>IF(AND(N(B32)&gt;0,ISNUMBER(B33)),B28-B33,"")</f>
         <v/>
       </c>
     </row>
@@ -6503,7 +6603,7 @@
         </is>
       </c>
       <c r="B37" s="66">
-        <f>IFERROR(B34-B35,"")</f>
+        <f>IF(AND(ISNUMBER(B34),ISNUMBER(B35)),B34-B35,"")</f>
         <v/>
       </c>
     </row>
@@ -6514,7 +6614,7 @@
         </is>
       </c>
       <c r="B38" s="56">
-        <f>IF(B34="","",IF(B34&gt;B35,"market prices in MORE growth than history delivered","market prices in LESS growth than history delivered"))</f>
+        <f>IF(OR(NOT(ISNUMBER(B34)),NOT(ISNUMBER(B35))),"",IF(B34&gt;B35,"market prices in MORE growth than history delivered","market prices in LESS growth than history delivered"))</f>
         <v/>
       </c>
     </row>
@@ -6532,7 +6632,7 @@
         </is>
       </c>
       <c r="B41" s="66">
-        <f>IFERROR((B28-0.01)-B33,"")</f>
+        <f>IF(ISNUMBER(B34),(B28-0.01)-B33,"")</f>
         <v/>
       </c>
     </row>
@@ -6554,7 +6654,7 @@
         </is>
       </c>
       <c r="B43" s="66">
-        <f>IFERROR((B28+0.01)-B33,"")</f>
+        <f>IF(ISNUMBER(B34),(B28+0.01)-B33,"")</f>
         <v/>
       </c>
     </row>
@@ -6751,41 +6851,10 @@
         <f>_xll.TR("PEERS("&amp;Snapshot!$B$3&amp;")",_xlfn._LONGTEXT("TR.CommonName;TR.PriceClose;TR.CompanyMarketCap(Scale=6);TR.PE;TR.EVToEBITDA;TR.PriceToSalesPerShare;TR.GrossMargin;TR.NetProfitMargin;TR.FreeOperatingCashFlowExclDividends(Period=LTM,SDate=0D,Curn=USD)/TR.CompanyMarketCap(SDate=0D,Curn=USD)*100/*Free Cas","h Flow Yield*/;TR.NetDebt/TR.EBITDA(Period=LTM)/*Net Debt to EBITDA*/;TR.Revenue(Period=LTM,Scale=6)/*Rev LTM (now)*/;TR.Revenue(Period=LTM-3,Scale=6)/*Rev LTM (-3)*/"))</f>
         <v/>
       </c>
-      <c r="B5" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1027.96921834819</v>
-      </c>
-      <c r="D5" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E5" s="38" t="n">
-        <v>14.796323073741</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.099641239119045</v>
-      </c>
-      <c r="G5" t="n">
-        <v>28.00054</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.65055</v>
-      </c>
-      <c r="I5" s="38" t="n">
-        <v>53.1438400438431</v>
-      </c>
-      <c r="J5" s="38" t="n">
-        <v>6.8556654676259</v>
-      </c>
-      <c r="K5" t="n">
-        <v>10307</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7865.2</v>
-      </c>
+      <c r="D5" s="38" t="n"/>
+      <c r="E5" s="38" t="n"/>
+      <c r="I5" s="38" t="n"/>
+      <c r="J5" s="38" t="n"/>
       <c r="M5" s="84">
         <f>IFERROR(((K5/L5)^(1/3)-1)*100,"")</f>
         <v/>
@@ -6826,14 +6895,7 @@
         <f>_xll.TR("PEERS("&amp;Snapshot!$B$3&amp;")","TR.CommonName;TR.FwdPE;TR.FwdPEG")</f>
         <v/>
       </c>
-      <c r="X5" t="n">
-        <v>11.7586900709423</v>
-      </c>
-      <c r="Y5" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="Y5" s="38" t="n"/>
       <c r="Z5">
         <f>IF(AND($W5=$A5,ISNUMBER($X5)),$X5,"")</f>
         <v/>
@@ -6845,46 +6907,11 @@
       <c r="AB5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
-        <is>
-          <t>Nintendo Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>8839</v>
-      </c>
-      <c r="C6" t="n">
-        <v>11410956.7989832</v>
-      </c>
-      <c r="D6" s="38" t="n">
-        <v>21.5690728143982</v>
-      </c>
-      <c r="E6" s="38" t="n">
-        <v>20.1520130615391</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5.03789510830414</v>
-      </c>
-      <c r="G6" t="n">
-        <v>39.29689</v>
-      </c>
-      <c r="H6" t="n">
-        <v>18.33319</v>
-      </c>
-      <c r="I6" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="J6" s="38" t="n">
-        <v>-4.72825360798253</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2258501</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1755558</v>
-      </c>
+      <c r="A6" s="38" t="n"/>
+      <c r="D6" s="38" t="n"/>
+      <c r="E6" s="38" t="n"/>
+      <c r="I6" s="38" t="n"/>
+      <c r="J6" s="38" t="n"/>
       <c r="M6" s="84">
         <f>IFERROR(((K6/L6)^(1/3)-1)*100,"")</f>
         <v/>
@@ -6921,17 +6948,7 @@
         <f>IF(ISNUMBER(M6),M6,"")</f>
         <v/>
       </c>
-      <c r="W6" s="38" t="inlineStr">
-        <is>
-          <t>Nintendo Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="X6" t="n">
-        <v>22.6497781198561</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.12685463282866</v>
-      </c>
+      <c r="W6" s="38" t="n"/>
       <c r="Z6">
         <f>IF(AND($W6=$A6,ISNUMBER($X6)),$X6,"")</f>
         <v/>
@@ -6942,44 +6959,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="inlineStr">
-        <is>
-          <t>Best Buy Co., Inc.</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>90.27</v>
-      </c>
-      <c r="C7" t="n">
-        <v>19025.94846402</v>
-      </c>
-      <c r="D7" s="38" t="n">
-        <v>14.9861792464576</v>
-      </c>
-      <c r="E7" s="38" t="n">
-        <v>6.76468644947963</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.45084117589678</v>
-      </c>
-      <c r="G7" t="n">
-        <v>22.48207</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.5641</v>
-      </c>
-      <c r="I7" s="38" t="n">
-        <v>9.587844251453911</v>
-      </c>
-      <c r="J7" s="38" t="n">
-        <v>-0.211915535444947</v>
-      </c>
-      <c r="K7" t="n">
-        <v>42201</v>
-      </c>
-      <c r="L7" t="n">
-        <v>44372</v>
-      </c>
+      <c r="A7" s="38" t="n"/>
+      <c r="D7" s="38" t="n"/>
+      <c r="E7" s="38" t="n"/>
+      <c r="I7" s="38" t="n"/>
+      <c r="J7" s="38" t="n"/>
       <c r="M7" s="84">
         <f>IFERROR(((K7/L7)^(1/3)-1)*100,"")</f>
         <v/>
@@ -7016,17 +7000,7 @@
         <f>IF(ISNUMBER(M7),M7,"")</f>
         <v/>
       </c>
-      <c r="W7" s="38" t="inlineStr">
-        <is>
-          <t>Best Buy Co., Inc.</t>
-        </is>
-      </c>
-      <c r="X7" t="n">
-        <v>12.843851804846</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.62119424588693</v>
-      </c>
+      <c r="W7" s="38" t="n"/>
       <c r="Z7">
         <f>IF(AND($W7=$A7,ISNUMBER($X7)),$X7,"")</f>
         <v/>
@@ -7037,44 +7011,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
-        <is>
-          <t>Sony Group Corporation</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3885</v>
-      </c>
-      <c r="C8" t="n">
-        <v>23242195.7345011</v>
-      </c>
-      <c r="D8" s="38" t="n">
-        <v>20.8079215141268</v>
-      </c>
-      <c r="E8" t="n">
-        <v>8.29645378287006</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.82543027905581</v>
-      </c>
-      <c r="G8" s="38" t="n">
-        <v>31.2441</v>
-      </c>
-      <c r="H8" t="n">
-        <v>8.26061</v>
-      </c>
-      <c r="I8" s="38" t="n">
-        <v>6.8481806935447</v>
-      </c>
-      <c r="J8" s="38" t="n">
-        <v>-0.061661978354665</v>
-      </c>
-      <c r="K8" t="n">
-        <v>12695776</v>
-      </c>
-      <c r="L8" t="n">
-        <v>11708265</v>
-      </c>
+      <c r="A8" s="38" t="n"/>
+      <c r="D8" s="38" t="n"/>
+      <c r="G8" s="38" t="n"/>
+      <c r="I8" s="38" t="n"/>
+      <c r="J8" s="38" t="n"/>
       <c r="M8" s="84">
         <f>IFERROR(((K8/L8)^(1/3)-1)*100,"")</f>
         <v/>
@@ -7111,17 +7052,7 @@
         <f>IF(ISNUMBER(M8),M8,"")</f>
         <v/>
       </c>
-      <c r="W8" s="38" t="inlineStr">
-        <is>
-          <t>Sony Group Corporation</t>
-        </is>
-      </c>
-      <c r="X8" t="n">
-        <v>17.5627937779793</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.37335051053775</v>
-      </c>
+      <c r="W8" s="38" t="n"/>
       <c r="Z8">
         <f>IF(AND($W8=$A8,ISNUMBER($X8)),$X8,"")</f>
         <v/>
@@ -7132,44 +7063,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
-        <is>
-          <t>Carrefour SA</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>16.405</v>
-      </c>
-      <c r="C9" t="n">
-        <v>12090.6172408997</v>
-      </c>
-      <c r="D9" t="n">
-        <v>7.96173707097375</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7.03343196003482</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.147928432859129</v>
-      </c>
-      <c r="G9" t="n">
-        <v>19.07051</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.16037</v>
-      </c>
-      <c r="I9" s="38" t="n">
-        <v>21.2082646897647</v>
-      </c>
-      <c r="J9" s="38" t="n">
-        <v>3.66866746698679</v>
-      </c>
-      <c r="K9" t="n">
-        <v>81656</v>
-      </c>
-      <c r="L9" t="n">
-        <v>84838</v>
-      </c>
+      <c r="A9" s="38" t="n"/>
+      <c r="I9" s="38" t="n"/>
+      <c r="J9" s="38" t="n"/>
       <c r="M9" s="84">
         <f>IFERROR(((K9/L9)^(1/3)-1)*100,"")</f>
         <v/>
@@ -7206,17 +7102,7 @@
         <f>IF(ISNUMBER(M9),M9,"")</f>
         <v/>
       </c>
-      <c r="W9" s="38" t="inlineStr">
-        <is>
-          <t>Carrefour SA</t>
-        </is>
-      </c>
-      <c r="X9" t="n">
-        <v>9.018238550010841</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.30699109420447</v>
-      </c>
+      <c r="W9" s="38" t="n"/>
       <c r="Z9">
         <f>IF(AND($W9=$A9,ISNUMBER($X9)),$X9,"")</f>
         <v/>
@@ -7228,44 +7114,12 @@
       <c r="AB9" s="38" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
-        <is>
-          <t>Target Corp</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>164.44</v>
-      </c>
-      <c r="C10" t="n">
-        <v>74704.55526784</v>
-      </c>
-      <c r="D10" s="38" t="n">
-        <v>17.0697249058746</v>
-      </c>
-      <c r="E10" s="38" t="n">
-        <v>10.0499293918841</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.693603409942343</v>
-      </c>
-      <c r="G10" s="38" t="n">
-        <v>27.93377</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.53598</v>
-      </c>
-      <c r="I10" s="38" t="n">
-        <v>5.98046891017042</v>
-      </c>
-      <c r="J10" s="38" t="n">
-        <v>1.40365665439867</v>
-      </c>
-      <c r="K10" t="n">
-        <v>107705</v>
-      </c>
-      <c r="L10" t="n">
-        <v>108008</v>
-      </c>
+      <c r="A10" s="38" t="n"/>
+      <c r="D10" s="38" t="n"/>
+      <c r="E10" s="38" t="n"/>
+      <c r="G10" s="38" t="n"/>
+      <c r="I10" s="38" t="n"/>
+      <c r="J10" s="38" t="n"/>
       <c r="M10" s="84">
         <f>IFERROR(((K10/L10)^(1/3)-1)*100,"")</f>
         <v/>
@@ -7302,17 +7156,7 @@
         <f>IF(ISNUMBER(M10),M10,"")</f>
         <v/>
       </c>
-      <c r="W10" s="38" t="inlineStr">
-        <is>
-          <t>Target Corp</t>
-        </is>
-      </c>
-      <c r="X10" t="n">
-        <v>16.5475679376016</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.79864868886974</v>
-      </c>
+      <c r="W10" s="38" t="n"/>
       <c r="Z10">
         <f>IF(AND($W10=$A10,ISNUMBER($X10)),$X10,"")</f>
         <v/>
@@ -7323,44 +7167,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>499.7</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3787919.26586892</v>
-      </c>
-      <c r="D11" s="38" t="n">
-        <v>27.843621041464</v>
-      </c>
-      <c r="E11" t="n">
-        <v>19.6461006698103</v>
-      </c>
-      <c r="F11" t="n">
-        <v>11.1817630894883</v>
-      </c>
-      <c r="G11" s="38" t="n">
-        <v>67.94409</v>
-      </c>
-      <c r="H11" t="n">
-        <v>40.30539</v>
-      </c>
-      <c r="I11" s="38" t="n">
-        <v>1.76843790213764</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.154602571821115</v>
-      </c>
-      <c r="K11" t="n">
-        <v>331839</v>
-      </c>
-      <c r="L11" t="n">
-        <v>211915</v>
-      </c>
+      <c r="A11" s="38" t="n"/>
+      <c r="D11" s="38" t="n"/>
+      <c r="G11" s="38" t="n"/>
+      <c r="I11" s="38" t="n"/>
       <c r="M11" s="84">
         <f>IFERROR(((K11/L11)^(1/3)-1)*100,"")</f>
         <v/>
@@ -7397,17 +7207,7 @@
         <f>IF(ISNUMBER(M11),M11,"")</f>
         <v/>
       </c>
-      <c r="W11" s="38" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="X11" t="n">
-        <v>24.512847126284</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.47371855943963</v>
-      </c>
+      <c r="W11" s="38" t="n"/>
       <c r="Z11">
         <f>IF(AND($W11=$A11,ISNUMBER($X11)),$X11,"")</f>
         <v/>
@@ -7418,44 +7218,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="73" t="inlineStr">
-        <is>
-          <t>Walmart Inc</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>107.14</v>
-      </c>
-      <c r="C12" t="n">
-        <v>860176.7674492199</v>
-      </c>
-      <c r="D12" t="n">
-        <v>38.8181373525842</v>
-      </c>
-      <c r="E12" t="n">
-        <v>20.2438658941988</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.15517173877574</v>
-      </c>
-      <c r="G12" t="n">
-        <v>24.9267</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.06985</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.57049114916923</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.05071772458013</v>
-      </c>
-      <c r="K12" t="n">
-        <v>735840</v>
-      </c>
-      <c r="L12" t="n">
-        <v>630794</v>
-      </c>
+      <c r="A12" s="73" t="n"/>
       <c r="M12" s="84">
         <f>IFERROR(((K12/L12)^(1/3)-1)*100,"")</f>
         <v/>
@@ -7492,17 +7255,7 @@
         <f>IF(ISNUMBER(M12),M12,"")</f>
         <v/>
       </c>
-      <c r="W12" s="38" t="inlineStr">
-        <is>
-          <t>Walmart Inc</t>
-        </is>
-      </c>
-      <c r="X12" t="n">
-        <v>34.7323285825216</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>3.68024673722083</v>
-      </c>
+      <c r="W12" s="38" t="n"/>
       <c r="Z12">
         <f>IF(AND($W12=$A12,ISNUMBER($X12)),$X12,"")</f>
         <v/>
@@ -7513,44 +7266,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="inlineStr">
-        <is>
-          <t>Amazon.com Inc</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>258.51</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2792576.5837908</v>
-      </c>
-      <c r="D13" s="38" t="n">
-        <v>20.7928652264243</v>
-      </c>
-      <c r="E13" t="n">
-        <v>15.9669435332564</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3.59474257618828</v>
-      </c>
-      <c r="G13" s="38" t="n">
-        <v>50.28566</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10.83378</v>
-      </c>
-      <c r="I13" s="38" t="n">
-        <v>-0.416282227226133</v>
-      </c>
-      <c r="J13" s="38" t="n">
-        <v>-0.19067159539232</v>
-      </c>
-      <c r="K13" t="n">
-        <v>775680</v>
-      </c>
-      <c r="L13" t="n">
-        <v>538046</v>
-      </c>
+      <c r="A13" s="38" t="n"/>
+      <c r="D13" s="38" t="n"/>
+      <c r="G13" s="38" t="n"/>
+      <c r="I13" s="38" t="n"/>
+      <c r="J13" s="38" t="n"/>
       <c r="M13" s="84">
         <f>IFERROR(((K13/L13)^(1/3)-1)*100,"")</f>
         <v/>
@@ -7587,17 +7307,8 @@
         <f>IF(ISNUMBER(M13),M13,"")</f>
         <v/>
       </c>
-      <c r="W13" s="38" t="inlineStr">
-        <is>
-          <t>Amazon.com Inc</t>
-        </is>
-      </c>
-      <c r="X13" t="n">
-        <v>22.822263091419</v>
-      </c>
-      <c r="Y13" s="38" t="n">
-        <v>0.918400929232154</v>
-      </c>
+      <c r="W13" s="38" t="n"/>
+      <c r="Y13" s="38" t="n"/>
       <c r="Z13">
         <f>IF(AND($W13=$A13,ISNUMBER($X13)),$X13,"")</f>
         <v/>
@@ -7608,46 +7319,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
-        <is>
-          <t>ATRenew Inc</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="C14" t="n">
-        <v>917.5353684200001</v>
-      </c>
-      <c r="D14" s="38" t="n">
-        <v>14.0279933222827</v>
-      </c>
-      <c r="E14" s="38" t="n">
-        <v>7.34575754740216</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.255001783354496</v>
-      </c>
-      <c r="G14" t="n">
-        <v>12.2887</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.5977</v>
-      </c>
-      <c r="I14" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>-2.24874193083464</v>
-      </c>
-      <c r="K14" t="n">
-        <v>24172.75</v>
-      </c>
-      <c r="L14" t="n">
-        <v>11352.654</v>
-      </c>
+      <c r="A14" s="38" t="n"/>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="38" t="n"/>
+      <c r="I14" s="38" t="n"/>
       <c r="M14" s="84">
         <f>IFERROR(((K14/L14)^(1/3)-1)*100,"")</f>
         <v/>
@@ -7684,19 +7359,8 @@
         <f>IF(ISNUMBER(M14),M14,"")</f>
         <v/>
       </c>
-      <c r="W14" s="38" t="inlineStr">
-        <is>
-          <t>ATRenew Inc</t>
-        </is>
-      </c>
-      <c r="X14" t="n">
-        <v>7.39856337432504</v>
-      </c>
-      <c r="Y14" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W14" s="38" t="n"/>
+      <c r="Y14" s="38" t="n"/>
       <c r="Z14">
         <f>IF(AND($W14=$A14,ISNUMBER($X14)),$X14,"")</f>
         <v/>
@@ -7707,54 +7371,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
-        <is>
-          <t>hhgregg Inc</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.0027808166</v>
-      </c>
-      <c r="D15" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E15" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F15" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G15" s="38" t="n">
-        <v>28.25421</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-2.79995</v>
-      </c>
-      <c r="I15" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="J15" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>1769.703</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2397.922</v>
-      </c>
+      <c r="A15" s="38" t="n"/>
+      <c r="D15" s="38" t="n"/>
+      <c r="E15" s="38" t="n"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="38" t="n"/>
+      <c r="I15" s="38" t="n"/>
+      <c r="J15" s="38" t="n"/>
       <c r="M15" s="84">
         <f>IFERROR(((K15/L15)^(1/3)-1)*100,"")</f>
         <v/>
@@ -7791,21 +7414,9 @@
         <f>IF(ISNUMBER(M15),M15,"")</f>
         <v/>
       </c>
-      <c r="W15" s="38" t="inlineStr">
-        <is>
-          <t>hhgregg Inc</t>
-        </is>
-      </c>
-      <c r="X15" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="Y15" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W15" s="38" t="n"/>
+      <c r="X15" s="38" t="n"/>
+      <c r="Y15" s="38" t="n"/>
       <c r="Z15">
         <f>IF(AND($W15=$A15,ISNUMBER($X15)),$X15,"")</f>
         <v/>
@@ -7816,52 +7427,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="inlineStr">
-        <is>
-          <t>Newegg Commerce Inc</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>15.32</v>
-      </c>
-      <c r="C16" t="n">
-        <v>321.32168</v>
-      </c>
-      <c r="D16" s="38" t="n">
-        <v>34.0353683462188</v>
-      </c>
-      <c r="E16" s="38" t="n">
-        <v>19.1806581875994</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.2336120396961</v>
-      </c>
-      <c r="G16" t="n">
-        <v>11.66256</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.33791</v>
-      </c>
-      <c r="I16" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="J16" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="K16" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="L16" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="A16" s="38" t="n"/>
+      <c r="D16" s="38" t="n"/>
+      <c r="E16" s="38" t="n"/>
+      <c r="I16" s="38" t="n"/>
+      <c r="J16" s="38" t="n"/>
+      <c r="K16" s="38" t="n"/>
+      <c r="L16" s="38" t="n"/>
       <c r="M16" s="84">
         <f>IFERROR(((K16/L16)^(1/3)-1)*100,"")</f>
         <v/>
@@ -7898,21 +7470,9 @@
         <f>IF(ISNUMBER(M16),M16,"")</f>
         <v/>
       </c>
-      <c r="W16" s="38" t="inlineStr">
-        <is>
-          <t>Newegg Commerce Inc</t>
-        </is>
-      </c>
-      <c r="X16" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="Y16" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W16" s="38" t="n"/>
+      <c r="X16" s="38" t="n"/>
+      <c r="Y16" s="38" t="n"/>
       <c r="Z16">
         <f>IF(AND($W16=$A16,ISNUMBER($X16)),$X16,"")</f>
         <v/>
@@ -7923,50 +7483,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="inlineStr">
-        <is>
-          <t>Simply Inc</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.0015500207</v>
-      </c>
-      <c r="D17" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E17" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F17" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>22.14989</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-14.05746</v>
-      </c>
-      <c r="I17" s="38" t="n">
-        <v>-738635.296935067</v>
-      </c>
-      <c r="J17" s="38" t="n">
-        <v>-0.6276806476617</v>
-      </c>
-      <c r="K17" t="n">
-        <v>79.111</v>
-      </c>
-      <c r="L17" s="38" t="n">
-        <v>19.245</v>
-      </c>
+      <c r="A17" s="38" t="n"/>
+      <c r="D17" s="38" t="n"/>
+      <c r="E17" s="38" t="n"/>
+      <c r="F17" s="38" t="n"/>
+      <c r="I17" s="38" t="n"/>
+      <c r="J17" s="38" t="n"/>
+      <c r="L17" s="38" t="n"/>
       <c r="M17" s="84">
         <f>IFERROR(((K17/L17)^(1/3)-1)*100,"")</f>
         <v/>
@@ -8003,21 +7526,9 @@
         <f>IF(ISNUMBER(M17),M17,"")</f>
         <v/>
       </c>
-      <c r="W17" s="38" t="inlineStr">
-        <is>
-          <t>Simply Inc</t>
-        </is>
-      </c>
-      <c r="X17" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="Y17" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W17" s="38" t="n"/>
+      <c r="X17" s="38" t="n"/>
+      <c r="Y17" s="38" t="n"/>
       <c r="Z17">
         <f>IF(AND($W17=$A17,ISNUMBER($X17)),$X17,"")</f>
         <v/>
@@ -8028,46 +7539,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="inlineStr">
-        <is>
-          <t>Advent-AWI Holdings Inc</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="C18" t="n">
-        <v>8.622233285064169</v>
-      </c>
-      <c r="D18" s="38" t="n">
-        <v>1260.00027999999</v>
-      </c>
-      <c r="E18" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1.56901708952281</v>
-      </c>
-      <c r="G18" t="n">
-        <v>43.85337</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.11187</v>
-      </c>
-      <c r="I18" s="38" t="n">
-        <v>13.7763715769636</v>
-      </c>
-      <c r="J18" s="38" t="n">
-        <v>13.4566840689764</v>
-      </c>
-      <c r="K18" s="38" t="n">
-        <v>5.47704</v>
-      </c>
-      <c r="L18" t="n">
-        <v>5.76001</v>
-      </c>
+      <c r="A18" s="38" t="n"/>
+      <c r="D18" s="38" t="n"/>
+      <c r="E18" s="38" t="n"/>
+      <c r="I18" s="38" t="n"/>
+      <c r="J18" s="38" t="n"/>
+      <c r="K18" s="38" t="n"/>
       <c r="M18" s="84">
         <f>IFERROR(((K18/L18)^(1/3)-1)*100,"")</f>
         <v/>
@@ -8104,21 +7581,9 @@
         <f>IF(ISNUMBER(M18),M18,"")</f>
         <v/>
       </c>
-      <c r="W18" s="38" t="inlineStr">
-        <is>
-          <t>Advent-AWI Holdings Inc</t>
-        </is>
-      </c>
-      <c r="X18" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="Y18" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W18" s="38" t="n"/>
+      <c r="X18" s="38" t="n"/>
+      <c r="Y18" s="38" t="n"/>
       <c r="Z18">
         <f>IF(AND($W18=$A18,ISNUMBER($X18)),$X18,"")</f>
         <v/>
@@ -8129,44 +7594,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="inlineStr">
-        <is>
-          <t>Sally Beauty Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1563.4922764</v>
-      </c>
-      <c r="D19" s="38" t="n">
-        <v>8.70394596256782</v>
-      </c>
-      <c r="E19" s="38" t="n">
-        <v>5.27887349058167</v>
-      </c>
-      <c r="F19" s="38" t="n">
-        <v>0.419266195098248</v>
-      </c>
-      <c r="G19" s="38" t="n">
-        <v>51.62197</v>
-      </c>
-      <c r="H19" s="38" t="n">
-        <v>5.29196</v>
-      </c>
-      <c r="I19" s="38" t="n">
-        <v>15.6430214197884</v>
-      </c>
-      <c r="J19" s="38" t="n">
-        <v>1.72157869582029</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3729.116</v>
-      </c>
-      <c r="L19" t="n">
-        <v>3769.235</v>
-      </c>
+      <c r="A19" s="38" t="n"/>
+      <c r="D19" s="38" t="n"/>
+      <c r="E19" s="38" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="38" t="n"/>
+      <c r="I19" s="38" t="n"/>
+      <c r="J19" s="38" t="n"/>
       <c r="M19" s="84">
         <f>IFERROR(((K19/L19)^(1/3)-1)*100,"")</f>
         <v/>
@@ -8203,19 +7638,8 @@
         <f>IF(ISNUMBER(M19),M19,"")</f>
         <v/>
       </c>
-      <c r="W19" s="38" t="inlineStr">
-        <is>
-          <t>Sally Beauty Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="X19" t="n">
-        <v>7.53631520552749</v>
-      </c>
-      <c r="Y19" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W19" s="38" t="n"/>
+      <c r="Y19" s="38" t="n"/>
       <c r="Z19">
         <f>IF(AND($W19=$A19,ISNUMBER($X19)),$X19,"")</f>
         <v/>
@@ -8226,44 +7650,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="inlineStr">
-        <is>
-          <t>AutoCanada Inc</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="C20" t="n">
-        <v>528.172916223711</v>
-      </c>
-      <c r="D20" s="38" t="n">
-        <v>239.941324392288</v>
-      </c>
-      <c r="E20" s="38" t="n">
-        <v>14.3109480078788</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.106877812730311</v>
-      </c>
-      <c r="G20" s="38" t="n">
-        <v>16.02804</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.43872</v>
-      </c>
-      <c r="I20" s="38" t="n">
-        <v>4.2889065234088</v>
-      </c>
-      <c r="J20" s="38" t="n">
-        <v>11.0496535586768</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4925.41</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6307.743</v>
-      </c>
+      <c r="A20" s="38" t="n"/>
+      <c r="D20" s="38" t="n"/>
+      <c r="E20" s="38" t="n"/>
+      <c r="G20" s="38" t="n"/>
+      <c r="I20" s="38" t="n"/>
+      <c r="J20" s="38" t="n"/>
       <c r="M20" s="84">
         <f>IFERROR(((K20/L20)^(1/3)-1)*100,"")</f>
         <v/>
@@ -8300,19 +7692,8 @@
         <f>IF(ISNUMBER(M20),M20,"")</f>
         <v/>
       </c>
-      <c r="W20" s="38" t="inlineStr">
-        <is>
-          <t>AutoCanada Inc</t>
-        </is>
-      </c>
-      <c r="X20" t="n">
-        <v>9.796932896892089</v>
-      </c>
-      <c r="Y20" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W20" s="38" t="n"/>
+      <c r="Y20" s="38" t="n"/>
       <c r="Z20">
         <f>IF(AND($W20=$A20,ISNUMBER($X20)),$X20,"")</f>
         <v/>
@@ -8323,44 +7704,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="inlineStr">
-        <is>
-          <t>RH</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>147.99</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2800.89144579</v>
-      </c>
-      <c r="D21" s="38" t="n">
-        <v>28.5473435673473</v>
-      </c>
-      <c r="E21" s="38" t="n">
-        <v>12.103928678877</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.817560826369737</v>
-      </c>
-      <c r="G21" s="38" t="n">
-        <v>44.06865</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.62802</v>
-      </c>
-      <c r="I21" s="38" t="n">
-        <v>8.23494312949005</v>
-      </c>
-      <c r="J21" s="38" t="n">
-        <v>6.36152263080127</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3425.912</v>
-      </c>
-      <c r="L21" t="n">
-        <v>3372.347</v>
-      </c>
+      <c r="A21" s="38" t="n"/>
+      <c r="D21" s="38" t="n"/>
+      <c r="E21" s="38" t="n"/>
+      <c r="G21" s="38" t="n"/>
+      <c r="I21" s="38" t="n"/>
+      <c r="J21" s="38" t="n"/>
       <c r="M21" s="84">
         <f>IFERROR(((K21/L21)^(1/3)-1)*100,"")</f>
         <v/>
@@ -8397,19 +7746,8 @@
         <f>IF(ISNUMBER(M21),M21,"")</f>
         <v/>
       </c>
-      <c r="W21" s="38" t="inlineStr">
-        <is>
-          <t>RH</t>
-        </is>
-      </c>
-      <c r="X21" t="n">
-        <v>19.6368966288334</v>
-      </c>
-      <c r="Y21" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W21" s="38" t="n"/>
+      <c r="Y21" s="38" t="n"/>
       <c r="Z21">
         <f>IF(AND($W21=$A21,ISNUMBER($X21)),$X21,"")</f>
         <v/>
@@ -8420,44 +7758,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="inlineStr">
-        <is>
-          <t>Designer Brands Inc.</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="C22" t="n">
-        <v>267.08743554</v>
-      </c>
-      <c r="D22" s="38" t="n">
-        <v>27.8174414300069</v>
-      </c>
-      <c r="E22" s="38" t="n">
-        <v>5.32119019263565</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.09203209095307099</v>
-      </c>
-      <c r="G22" t="n">
-        <v>43.57184</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-0.28949</v>
-      </c>
-      <c r="I22" s="38" t="n">
-        <v>28.2781822708949</v>
-      </c>
-      <c r="J22" s="38" t="n">
-        <v>3.21301571521432</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2902.112</v>
-      </c>
-      <c r="L22" t="n">
-        <v>3226.967</v>
-      </c>
+      <c r="A22" s="38" t="n"/>
+      <c r="D22" s="38" t="n"/>
+      <c r="E22" s="38" t="n"/>
+      <c r="I22" s="38" t="n"/>
+      <c r="J22" s="38" t="n"/>
       <c r="M22" s="84">
         <f>IFERROR(((K22/L22)^(1/3)-1)*100,"")</f>
         <v/>
@@ -8494,19 +7799,8 @@
         <f>IF(ISNUMBER(M22),M22,"")</f>
         <v/>
       </c>
-      <c r="W22" s="38" t="inlineStr">
-        <is>
-          <t>Designer Brands Inc.</t>
-        </is>
-      </c>
-      <c r="X22" t="n">
-        <v>10.4518478896875</v>
-      </c>
-      <c r="Y22" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W22" s="38" t="n"/>
+      <c r="Y22" s="38" t="n"/>
       <c r="Z22">
         <f>IF(AND($W22=$A22,ISNUMBER($X22)),$X22,"")</f>
         <v/>
@@ -8517,44 +7811,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="inlineStr">
-        <is>
-          <t>Aritzia Inc.</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>128.67</v>
-      </c>
-      <c r="C23" t="n">
-        <v>12426.1964019256</v>
-      </c>
-      <c r="D23" s="38" t="n">
-        <v>33.7219115111044</v>
-      </c>
-      <c r="E23" s="38" t="n">
-        <v>15.8817383445171</v>
-      </c>
-      <c r="F23" t="n">
-        <v>3.10410527779678</v>
-      </c>
-      <c r="G23" t="n">
-        <v>44.87484</v>
-      </c>
-      <c r="H23" t="n">
-        <v>10.31423</v>
-      </c>
-      <c r="I23" s="38" t="n">
-        <v>4.14499956184653</v>
-      </c>
-      <c r="J23" s="38" t="n">
-        <v>0.491797606051154</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3989.841</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2250.385</v>
-      </c>
+      <c r="A23" s="38" t="n"/>
+      <c r="D23" s="38" t="n"/>
+      <c r="E23" s="38" t="n"/>
+      <c r="I23" s="38" t="n"/>
+      <c r="J23" s="38" t="n"/>
       <c r="M23" s="84">
         <f>IFERROR(((K23/L23)^(1/3)-1)*100,"")</f>
         <v/>
@@ -8591,19 +7852,8 @@
         <f>IF(ISNUMBER(M23),M23,"")</f>
         <v/>
       </c>
-      <c r="W23" s="38" t="inlineStr">
-        <is>
-          <t>Aritzia Inc.</t>
-        </is>
-      </c>
-      <c r="X23" t="n">
-        <v>23.6910944944287</v>
-      </c>
-      <c r="Y23" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W23" s="38" t="n"/>
+      <c r="Y23" s="38" t="n"/>
       <c r="Z23">
         <f>IF(AND($W23=$A23,ISNUMBER($X23)),$X23,"")</f>
         <v/>
@@ -8614,44 +7864,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="inlineStr">
-        <is>
-          <t>LuxExperience BV</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1059.65961376</v>
-      </c>
-      <c r="D24" s="38" t="n">
-        <v>2.0236073345968</v>
-      </c>
-      <c r="E24" s="38" t="n">
-        <v>1.1065845672797</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.374537667065982</v>
-      </c>
-      <c r="G24" s="38" t="n">
-        <v>48.1106</v>
-      </c>
-      <c r="H24" t="n">
-        <v>45.15324</v>
-      </c>
-      <c r="I24" s="38" t="n">
-        <v>-15.91953331465</v>
-      </c>
-      <c r="J24" s="38" t="n">
-        <v>-0.537345655737934</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2433.973</v>
-      </c>
-      <c r="L24" t="n">
-        <v>737.732</v>
-      </c>
+      <c r="A24" s="38" t="n"/>
+      <c r="D24" s="38" t="n"/>
+      <c r="E24" s="38" t="n"/>
+      <c r="G24" s="38" t="n"/>
+      <c r="I24" s="38" t="n"/>
+      <c r="J24" s="38" t="n"/>
       <c r="M24" s="84">
         <f>IFERROR(((K24/L24)^(1/3)-1)*100,"")</f>
         <v/>
@@ -8688,21 +7906,9 @@
         <f>IF(ISNUMBER(M24),M24,"")</f>
         <v/>
       </c>
-      <c r="W24" s="38" t="inlineStr">
-        <is>
-          <t>LuxExperience BV</t>
-        </is>
-      </c>
-      <c r="X24" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="Y24" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W24" s="38" t="n"/>
+      <c r="X24" s="38" t="n"/>
+      <c r="Y24" s="38" t="n"/>
       <c r="Z24">
         <f>IF(AND($W24=$A24,ISNUMBER($X24)),$X24,"")</f>
         <v/>
@@ -8713,44 +7919,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="38" t="inlineStr">
-        <is>
-          <t>Caleres Inc</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="C25" t="n">
-        <v>417.52051792</v>
-      </c>
-      <c r="D25" s="38" t="n">
-        <v>1075.25951557094</v>
-      </c>
-      <c r="E25" s="38" t="n">
-        <v>7.03566314765152</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.148571600669127</v>
-      </c>
-      <c r="G25" t="n">
-        <v>42.96016</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-0.24265</v>
-      </c>
-      <c r="I25" s="38" t="n">
-        <v>5.41753386263946</v>
-      </c>
-      <c r="J25" s="38" t="n">
-        <v>2.62274921461957</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2810.231</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2895.756</v>
-      </c>
+      <c r="A25" s="38" t="n"/>
+      <c r="D25" s="38" t="n"/>
+      <c r="E25" s="38" t="n"/>
+      <c r="I25" s="38" t="n"/>
+      <c r="J25" s="38" t="n"/>
       <c r="M25" s="84">
         <f>IFERROR(((K25/L25)^(1/3)-1)*100,"")</f>
         <v/>
@@ -8787,19 +7960,8 @@
         <f>IF(ISNUMBER(M25),M25,"")</f>
         <v/>
       </c>
-      <c r="W25" s="38" t="inlineStr">
-        <is>
-          <t>Caleres Inc</t>
-        </is>
-      </c>
-      <c r="X25" t="n">
-        <v>6.20607163504225</v>
-      </c>
-      <c r="Y25" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W25" s="38" t="n"/>
+      <c r="Y25" s="38" t="n"/>
       <c r="Z25">
         <f>IF(AND($W25=$A25,ISNUMBER($X25)),$X25,"")</f>
         <v/>
@@ -8810,44 +7972,14 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="38" t="inlineStr">
-        <is>
-          <t>Floor &amp; Decor Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>50.23</v>
-      </c>
-      <c r="C26" t="n">
-        <v>5348.99094195</v>
-      </c>
-      <c r="D26" s="38" t="n">
-        <v>23.436479349023</v>
-      </c>
-      <c r="E26" s="38" t="n">
-        <v>9.628594230535271</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1.13524603022956</v>
-      </c>
-      <c r="G26" s="38" t="n">
-        <v>43.63513</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4.45438</v>
-      </c>
-      <c r="I26" s="38" t="n">
-        <v>4.0201203055695</v>
-      </c>
-      <c r="J26" s="38" t="n">
-        <v>-0.09783602447836</v>
-      </c>
-      <c r="K26" s="38" t="n">
-        <v>4711.746</v>
-      </c>
-      <c r="L26" s="38" t="n">
-        <v>4403.844</v>
-      </c>
+      <c r="A26" s="38" t="n"/>
+      <c r="D26" s="38" t="n"/>
+      <c r="E26" s="38" t="n"/>
+      <c r="G26" s="38" t="n"/>
+      <c r="I26" s="38" t="n"/>
+      <c r="J26" s="38" t="n"/>
+      <c r="K26" s="38" t="n"/>
+      <c r="L26" s="38" t="n"/>
       <c r="M26" s="84">
         <f>IFERROR(((K26/L26)^(1/3)-1)*100,"")</f>
         <v/>
@@ -8884,17 +8016,8 @@
         <f>IF(ISNUMBER(M26),M26,"")</f>
         <v/>
       </c>
-      <c r="W26" s="38" t="inlineStr">
-        <is>
-          <t>Floor &amp; Decor Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="X26" t="n">
-        <v>23.5103339631793</v>
-      </c>
-      <c r="Y26" s="38" t="n">
-        <v>3.15574952525897</v>
-      </c>
+      <c r="W26" s="38" t="n"/>
+      <c r="Y26" s="38" t="n"/>
       <c r="Z26">
         <f>IF(AND($W26=$A26,ISNUMBER($X26)),$X26,"")</f>
         <v/>
@@ -8905,44 +8028,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="38" t="inlineStr">
-        <is>
-          <t>Upbound Group, Inc.</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1088.44989135</v>
-      </c>
-      <c r="D27" s="38" t="n">
-        <v>12.343912591051</v>
-      </c>
-      <c r="E27" t="n">
-        <v>5.61088756731742</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.233231191528728</v>
-      </c>
-      <c r="G27" t="n">
-        <v>48.38508</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.55998</v>
-      </c>
-      <c r="I27" s="38" t="n">
-        <v>35.3237207385937</v>
-      </c>
-      <c r="J27" s="38" t="n">
-        <v>3.37894054618616</v>
-      </c>
-      <c r="K27" s="38" t="n">
-        <v>4744.317</v>
-      </c>
-      <c r="L27" t="n">
-        <v>4009.64</v>
-      </c>
+      <c r="A27" s="38" t="n"/>
+      <c r="D27" s="38" t="n"/>
+      <c r="I27" s="38" t="n"/>
+      <c r="J27" s="38" t="n"/>
+      <c r="K27" s="38" t="n"/>
       <c r="M27" s="84">
         <f>IFERROR(((K27/L27)^(1/3)-1)*100,"")</f>
         <v/>
@@ -8979,19 +8069,8 @@
         <f>IF(ISNUMBER(M27),M27,"")</f>
         <v/>
       </c>
-      <c r="W27" s="38" t="inlineStr">
-        <is>
-          <t>Upbound Group, Inc.</t>
-        </is>
-      </c>
-      <c r="X27" t="n">
-        <v>4.28300949415223</v>
-      </c>
-      <c r="Y27" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W27" s="38" t="n"/>
+      <c r="Y27" s="38" t="n"/>
       <c r="Z27">
         <f>IF(AND($W27=$A27,ISNUMBER($X27)),$X27,"")</f>
         <v/>
@@ -9002,48 +8081,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="38" t="inlineStr">
-        <is>
-          <t>Bob's Discount Furniture, Inc</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>17.64</v>
-      </c>
-      <c r="C28" t="n">
-        <v>2305.32002064</v>
-      </c>
-      <c r="D28" s="38" t="n">
-        <v>18.8925779158188</v>
-      </c>
-      <c r="E28" s="38" t="n">
-        <v>9.6167914695621</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.973514380734438</v>
-      </c>
-      <c r="G28" s="38" t="n">
-        <v>45.66377</v>
-      </c>
-      <c r="H28" t="n">
-        <v>5.14029</v>
-      </c>
-      <c r="I28" s="38" t="n">
-        <v>5.90660720413674</v>
-      </c>
-      <c r="J28" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>2463.412</v>
-      </c>
-      <c r="L28" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="A28" s="38" t="n"/>
+      <c r="D28" s="38" t="n"/>
+      <c r="E28" s="38" t="n"/>
+      <c r="G28" s="38" t="n"/>
+      <c r="I28" s="38" t="n"/>
+      <c r="J28" s="38" t="n"/>
+      <c r="L28" s="38" t="n"/>
       <c r="M28" s="84">
         <f>IFERROR(((K28/L28)^(1/3)-1)*100,"")</f>
         <v/>
@@ -9080,21 +8124,9 @@
         <f>IF(ISNUMBER(M28),M28,"")</f>
         <v/>
       </c>
-      <c r="W28" s="38" t="inlineStr">
-        <is>
-          <t>Bob's Discount Furniture, Inc</t>
-        </is>
-      </c>
-      <c r="X28" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="Y28" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W28" s="38" t="n"/>
+      <c r="X28" s="38" t="n"/>
+      <c r="Y28" s="38" t="n"/>
       <c r="Z28">
         <f>IF(AND($W28=$A28,ISNUMBER($X28)),$X28,"")</f>
         <v/>
@@ -9105,44 +8137,9 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="inlineStr">
-        <is>
-          <t>Genesco Inc</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>35.81</v>
-      </c>
-      <c r="C29" t="n">
-        <v>397.74070313</v>
-      </c>
-      <c r="D29" t="n">
-        <v>24.3048249930432</v>
-      </c>
-      <c r="E29" t="n">
-        <v>5.15006243750849</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.16239961943092</v>
-      </c>
-      <c r="G29" t="n">
-        <v>46.25639</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.54497</v>
-      </c>
-      <c r="I29" s="38" t="n">
-        <v>22.3389817278708</v>
-      </c>
-      <c r="J29" s="38" t="n">
-        <v>-1.25033670657721</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2449.148</v>
-      </c>
-      <c r="L29" t="n">
-        <v>2347.472</v>
-      </c>
+      <c r="A29" s="38" t="n"/>
+      <c r="I29" s="38" t="n"/>
+      <c r="J29" s="38" t="n"/>
       <c r="M29" s="84">
         <f>IFERROR(((K29/L29)^(1/3)-1)*100,"")</f>
         <v/>
@@ -9179,19 +8176,8 @@
         <f>IF(ISNUMBER(M29),M29,"")</f>
         <v/>
       </c>
-      <c r="W29" s="38" t="inlineStr">
-        <is>
-          <t>Genesco Inc</t>
-        </is>
-      </c>
-      <c r="X29" t="n">
-        <v>13.5029088276526</v>
-      </c>
-      <c r="Y29" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W29" s="38" t="n"/>
+      <c r="Y29" s="38" t="n"/>
       <c r="Z29">
         <f>IF(AND($W29=$A29,ISNUMBER($X29)),$X29,"")</f>
         <v/>
@@ -9202,44 +8188,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="38" t="inlineStr">
-        <is>
-          <t>Five Below, Inc.</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>252.2</v>
-      </c>
-      <c r="C30" t="n">
-        <v>13268.67242596</v>
-      </c>
-      <c r="D30" s="38" t="n">
-        <v>22.6276822147495</v>
-      </c>
-      <c r="E30" t="n">
-        <v>12.277515613669</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2.62435715794973</v>
-      </c>
-      <c r="G30" t="n">
-        <v>35.99146</v>
-      </c>
-      <c r="H30" t="n">
-        <v>7.52792</v>
-      </c>
-      <c r="I30" s="38" t="n">
-        <v>4.51627699262192</v>
-      </c>
-      <c r="J30" s="38" t="n">
-        <v>-0.947388907238497</v>
-      </c>
-      <c r="K30" t="n">
-        <v>5313.868</v>
-      </c>
-      <c r="L30" t="n">
-        <v>3253.013</v>
-      </c>
+      <c r="A30" s="38" t="n"/>
+      <c r="D30" s="38" t="n"/>
+      <c r="I30" s="38" t="n"/>
+      <c r="J30" s="38" t="n"/>
       <c r="M30" s="84">
         <f>IFERROR(((K30/L30)^(1/3)-1)*100,"")</f>
         <v/>
@@ -9276,17 +8228,7 @@
         <f>IF(ISNUMBER(M30),M30,"")</f>
         <v/>
       </c>
-      <c r="W30" s="38" t="inlineStr">
-        <is>
-          <t>Five Below, Inc.</t>
-        </is>
-      </c>
-      <c r="X30" t="n">
-        <v>23.5603422331057</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.44423868291181</v>
-      </c>
+      <c r="W30" s="38" t="n"/>
       <c r="Z30">
         <f>IF(AND($W30=$A30,ISNUMBER($X30)),$X30,"")</f>
         <v/>
@@ -9297,50 +8239,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="38" t="inlineStr">
-        <is>
-          <t>Farfetch Ltd</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.000352607954</v>
-      </c>
-      <c r="D31" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E31" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F31" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>44.16557</v>
-      </c>
-      <c r="H31" t="n">
-        <v>15.5087</v>
-      </c>
-      <c r="I31" s="38" t="n">
-        <v>-124589929.131321</v>
-      </c>
-      <c r="J31" s="38" t="n">
-        <v>-1.41298298447426</v>
-      </c>
-      <c r="K31" s="38" t="n">
-        <v>2351.007</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1333.83</v>
-      </c>
+      <c r="A31" s="38" t="n"/>
+      <c r="D31" s="38" t="n"/>
+      <c r="E31" s="38" t="n"/>
+      <c r="F31" s="38" t="n"/>
+      <c r="I31" s="38" t="n"/>
+      <c r="J31" s="38" t="n"/>
+      <c r="K31" s="38" t="n"/>
       <c r="M31" s="84">
         <f>IFERROR(((K31/L31)^(1/3)-1)*100,"")</f>
         <v/>
@@ -9377,21 +8282,9 @@
         <f>IF(ISNUMBER(M31),M31,"")</f>
         <v/>
       </c>
-      <c r="W31" s="38" t="inlineStr">
-        <is>
-          <t>Farfetch Ltd</t>
-        </is>
-      </c>
-      <c r="X31" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="Y31" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W31" s="38" t="n"/>
+      <c r="X31" s="38" t="n"/>
+      <c r="Y31" s="38" t="n"/>
       <c r="Z31">
         <f>IF(AND($W31=$A31,ISNUMBER($X31)),$X31,"")</f>
         <v/>
@@ -9402,44 +8295,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="38" t="inlineStr">
-        <is>
-          <t>Boot Barn Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>154.29</v>
-      </c>
-      <c r="C32" t="n">
-        <v>4672.64858076</v>
-      </c>
-      <c r="D32" s="38" t="n">
-        <v>19.520767622019</v>
-      </c>
-      <c r="E32" s="38" t="n">
-        <v>11.7289414194061</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1.9940402946605</v>
-      </c>
-      <c r="G32" t="n">
-        <v>38.08379</v>
-      </c>
-      <c r="H32" t="n">
-        <v>10.02192</v>
-      </c>
-      <c r="I32" s="38" t="n">
-        <v>2.60833248650231</v>
-      </c>
-      <c r="J32" t="n">
-        <v>-0.329057039890001</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2343.307</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1675.454</v>
-      </c>
+      <c r="A32" s="38" t="n"/>
+      <c r="D32" s="38" t="n"/>
+      <c r="E32" s="38" t="n"/>
+      <c r="I32" s="38" t="n"/>
       <c r="M32" s="84">
         <f>IFERROR(((K32/L32)^(1/3)-1)*100,"")</f>
         <v/>
@@ -9476,17 +8335,7 @@
         <f>IF(ISNUMBER(M32),M32,"")</f>
         <v/>
       </c>
-      <c r="W32" s="38" t="inlineStr">
-        <is>
-          <t>Boot Barn Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="X32" t="n">
-        <v>16.2733082691004</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0.962917649059193</v>
-      </c>
+      <c r="W32" s="38" t="n"/>
       <c r="Z32">
         <f>IF(AND($W32=$A32,ISNUMBER($X32)),$X32,"")</f>
         <v/>
@@ -9497,44 +8346,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="38" t="inlineStr">
-        <is>
-          <t>MarineMax Inc</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>52.16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1152.0440976</v>
-      </c>
-      <c r="D33" s="38" t="n">
-        <v>360.918903957929</v>
-      </c>
-      <c r="E33" s="38" t="n">
-        <v>18.3933407568704</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.5246100059152971</v>
-      </c>
-      <c r="G33" t="n">
-        <v>32.48742</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-1.36973</v>
-      </c>
-      <c r="I33" s="38" t="n">
-        <v>15.452620292128</v>
-      </c>
-      <c r="J33" t="n">
-        <v>8.90448077789458</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2196.001</v>
-      </c>
-      <c r="L33" t="n">
-        <v>2336.875</v>
-      </c>
+      <c r="A33" s="38" t="n"/>
+      <c r="D33" s="38" t="n"/>
+      <c r="E33" s="38" t="n"/>
+      <c r="I33" s="38" t="n"/>
       <c r="M33" s="84">
         <f>IFERROR(((K33/L33)^(1/3)-1)*100,"")</f>
         <v/>
@@ -9571,19 +8386,9 @@
         <f>IF(ISNUMBER(M33),M33,"")</f>
         <v/>
       </c>
-      <c r="W33" s="38" t="inlineStr">
-        <is>
-          <t>MarineMax Inc</t>
-        </is>
-      </c>
-      <c r="X33" s="38" t="n">
-        <v>35.5074040070966</v>
-      </c>
-      <c r="Y33" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W33" s="38" t="n"/>
+      <c r="X33" s="38" t="n"/>
+      <c r="Y33" s="38" t="n"/>
       <c r="Z33">
         <f>IF(AND($W33=$A33,ISNUMBER($X33)),$X33,"")</f>
         <v/>
@@ -9594,44 +8399,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="38" t="inlineStr">
-        <is>
-          <t>Abercrombie &amp; Fitch Co.</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>149.67</v>
-      </c>
-      <c r="C34" t="n">
-        <v>6650.0940357</v>
-      </c>
-      <c r="D34" s="38" t="n">
-        <v>12.8193708084589</v>
-      </c>
-      <c r="E34" s="38" t="n">
-        <v>6.64326610127084</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1.24511888202637</v>
-      </c>
-      <c r="G34" s="38" t="n">
-        <v>61.47415</v>
-      </c>
-      <c r="H34" t="n">
-        <v>9.625769999999999</v>
-      </c>
-      <c r="I34" s="38" t="n">
-        <v>8.88187816703048</v>
-      </c>
-      <c r="J34" s="38" t="n">
-        <v>-0.846561663011011</v>
-      </c>
-      <c r="K34" t="n">
-        <v>5340.931</v>
-      </c>
-      <c r="L34" t="n">
-        <v>3851.237</v>
-      </c>
+      <c r="A34" s="38" t="n"/>
+      <c r="D34" s="38" t="n"/>
+      <c r="E34" s="38" t="n"/>
+      <c r="G34" s="38" t="n"/>
+      <c r="I34" s="38" t="n"/>
+      <c r="J34" s="38" t="n"/>
       <c r="M34" s="84">
         <f>IFERROR(((K34/L34)^(1/3)-1)*100,"")</f>
         <v/>
@@ -9668,17 +8441,7 @@
         <f>IF(ISNUMBER(M34),M34,"")</f>
         <v/>
       </c>
-      <c r="W34" s="38" t="inlineStr">
-        <is>
-          <t>Abercrombie &amp; Fitch Co.</t>
-        </is>
-      </c>
-      <c r="X34" t="n">
-        <v>11.5330440252068</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.74743091291012</v>
-      </c>
+      <c r="W34" s="38" t="n"/>
       <c r="Z34">
         <f>IF(AND($W34=$A34,ISNUMBER($X34)),$X34,"")</f>
         <v/>
@@ -9689,44 +8452,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="38" t="inlineStr">
-        <is>
-          <t>National Vision Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>16.74</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1333.89931031</v>
-      </c>
-      <c r="D35" s="38" t="n">
-        <v>27.0541082164329</v>
-      </c>
-      <c r="E35" s="38" t="n">
-        <v>8.23916510792295</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.650931137705528</v>
-      </c>
-      <c r="G35" t="n">
-        <v>58.76861</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1.48932</v>
-      </c>
-      <c r="I35" s="38" t="n">
-        <v>3.67928820568879</v>
-      </c>
-      <c r="J35" s="38" t="n">
-        <v>1.1117001014041</v>
-      </c>
-      <c r="K35" t="n">
-        <v>2033.426</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1504.007</v>
-      </c>
+      <c r="A35" s="38" t="n"/>
+      <c r="D35" s="38" t="n"/>
+      <c r="E35" s="38" t="n"/>
+      <c r="I35" s="38" t="n"/>
+      <c r="J35" s="38" t="n"/>
       <c r="M35" s="84">
         <f>IFERROR(((K35/L35)^(1/3)-1)*100,"")</f>
         <v/>
@@ -9763,17 +8493,8 @@
         <f>IF(ISNUMBER(M35),M35,"")</f>
         <v/>
       </c>
-      <c r="W35" s="38" t="inlineStr">
-        <is>
-          <t>National Vision Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="X35" t="n">
-        <v>14.5866148324367</v>
-      </c>
-      <c r="Y35" s="38" t="n">
-        <v>0.610318612235844</v>
-      </c>
+      <c r="W35" s="38" t="n"/>
+      <c r="Y35" s="38" t="n"/>
       <c r="Z35">
         <f>IF(AND($W35=$A35,ISNUMBER($X35)),$X35,"")</f>
         <v/>
@@ -9784,46 +8505,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="38" t="inlineStr">
-        <is>
-          <t>Valvoline Inc.</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="C36" t="n">
-        <v>4086.59296854</v>
-      </c>
-      <c r="D36" s="38" t="n">
-        <v>39.7192495132749</v>
-      </c>
-      <c r="E36" s="38" t="n">
-        <v>10.501017366573</v>
-      </c>
-      <c r="F36" t="n">
-        <v>2.08074998398167</v>
-      </c>
-      <c r="G36" t="n">
-        <v>38.50202</v>
-      </c>
-      <c r="H36" t="n">
-        <v>12.5592</v>
-      </c>
-      <c r="I36" t="n">
-        <v>3.34634807457202</v>
-      </c>
-      <c r="J36" s="38" t="n">
-        <v>2.37380550871276</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1964</v>
-      </c>
-      <c r="L36" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="A36" s="38" t="n"/>
+      <c r="D36" s="38" t="n"/>
+      <c r="E36" s="38" t="n"/>
+      <c r="J36" s="38" t="n"/>
+      <c r="L36" s="38" t="n"/>
       <c r="M36" s="84">
         <f>IFERROR(((K36/L36)^(1/3)-1)*100,"")</f>
         <v/>
@@ -9860,17 +8546,7 @@
         <f>IF(ISNUMBER(M36),M36,"")</f>
         <v/>
       </c>
-      <c r="W36" s="38" t="inlineStr">
-        <is>
-          <t>Valvoline Inc.</t>
-        </is>
-      </c>
-      <c r="X36" t="n">
-        <v>16.2633313851115</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.43923286593908</v>
-      </c>
+      <c r="W36" s="38" t="n"/>
       <c r="Z36">
         <f>IF(AND($W36=$A36,ISNUMBER($X36)),$X36,"")</f>
         <v/>
@@ -9881,48 +8557,14 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="38" t="inlineStr">
-        <is>
-          <t>Arko Petroleum Corp</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="C37" t="n">
-        <v>903.35853477</v>
-      </c>
-      <c r="D37" s="38" t="n">
-        <v>24.390243902439</v>
-      </c>
-      <c r="E37" s="38" t="n">
-        <v>7.92792971658688</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.151227500824892</v>
-      </c>
-      <c r="G37" s="38" t="n">
-        <v>5.07012</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.5863699999999999</v>
-      </c>
-      <c r="I37" s="38" t="n">
-        <v>3.67649930696965</v>
-      </c>
-      <c r="J37" s="38" t="n">
-        <v>3.20002569720577</v>
-      </c>
-      <c r="K37" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="L37" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="A37" s="38" t="n"/>
+      <c r="D37" s="38" t="n"/>
+      <c r="E37" s="38" t="n"/>
+      <c r="G37" s="38" t="n"/>
+      <c r="I37" s="38" t="n"/>
+      <c r="J37" s="38" t="n"/>
+      <c r="K37" s="38" t="n"/>
+      <c r="L37" s="38" t="n"/>
       <c r="M37" s="84">
         <f>IFERROR(((K37/L37)^(1/3)-1)*100,"")</f>
         <v/>
@@ -9959,21 +8601,9 @@
         <f>IF(ISNUMBER(M37),M37,"")</f>
         <v/>
       </c>
-      <c r="W37" s="38" t="inlineStr">
-        <is>
-          <t>Arko Petroleum Corp</t>
-        </is>
-      </c>
-      <c r="X37" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="Y37" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W37" s="38" t="n"/>
+      <c r="X37" s="38" t="n"/>
+      <c r="Y37" s="38" t="n"/>
       <c r="Z37">
         <f>IF(AND($W37=$A37,ISNUMBER($X37)),$X37,"")</f>
         <v/>
@@ -9984,44 +8614,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="38" t="inlineStr">
-        <is>
-          <t>Leon's Furniture Ltd</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>24.81</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1710.81142142248</v>
-      </c>
-      <c r="D38" s="38" t="n">
-        <v>10.82026411737</v>
-      </c>
-      <c r="E38" s="38" t="n">
-        <v>5.64553919715967</v>
-      </c>
-      <c r="F38" s="38" t="n">
-        <v>0.67169897375798</v>
-      </c>
-      <c r="G38" s="38" t="n">
-        <v>45.07845</v>
-      </c>
-      <c r="H38" s="38" t="n">
-        <v>6.10198</v>
-      </c>
-      <c r="I38" s="38" t="n">
-        <v>16.7523164363733</v>
-      </c>
-      <c r="J38" s="38" t="n">
-        <v>0.185455660865497</v>
-      </c>
-      <c r="K38" s="38" t="n">
-        <v>2538.524</v>
-      </c>
-      <c r="L38" s="38" t="n">
-        <v>2430.256</v>
-      </c>
+      <c r="A38" s="38" t="n"/>
+      <c r="D38" s="38" t="n"/>
+      <c r="E38" s="38" t="n"/>
+      <c r="F38" s="38" t="n"/>
+      <c r="G38" s="38" t="n"/>
+      <c r="H38" s="38" t="n"/>
+      <c r="I38" s="38" t="n"/>
+      <c r="J38" s="38" t="n"/>
+      <c r="K38" s="38" t="n"/>
+      <c r="L38" s="38" t="n"/>
       <c r="M38" s="84">
         <f>IFERROR(((K38/L38)^(1/3)-1)*100,"")</f>
         <v/>
@@ -10058,17 +8660,8 @@
         <f>IF(ISNUMBER(M38),M38,"")</f>
         <v/>
       </c>
-      <c r="W38" s="38" t="inlineStr">
-        <is>
-          <t>Leon's Furniture Ltd</t>
-        </is>
-      </c>
-      <c r="X38" t="n">
-        <v>10.8984007244867</v>
-      </c>
-      <c r="Y38" s="38" t="n">
-        <v>4.59848131834881</v>
-      </c>
+      <c r="W38" s="38" t="n"/>
+      <c r="Y38" s="38" t="n"/>
       <c r="Z38">
         <f>IF(AND($W38=$A38,ISNUMBER($X38)),$X38,"")</f>
         <v/>
@@ -10079,46 +8672,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="38" t="inlineStr">
-        <is>
-          <t>OneWater Marine Inc</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="C39" t="n">
-        <v>211.6533613</v>
-      </c>
-      <c r="D39" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E39" s="38" t="n">
-        <v>10.0003943624745</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.116697006836853</v>
-      </c>
-      <c r="G39" s="38" t="n">
-        <v>22.89239</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-6.11974</v>
-      </c>
-      <c r="I39" s="38" t="n">
-        <v>28.7860867546137</v>
-      </c>
-      <c r="J39" t="n">
-        <v>8.694480689662861</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1813.7</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1882.852</v>
-      </c>
+      <c r="A39" s="38" t="n"/>
+      <c r="D39" s="38" t="n"/>
+      <c r="E39" s="38" t="n"/>
+      <c r="G39" s="38" t="n"/>
+      <c r="I39" s="38" t="n"/>
       <c r="M39" s="84">
         <f>IFERROR(((K39/L39)^(1/3)-1)*100,"")</f>
         <v/>
@@ -10155,19 +8713,8 @@
         <f>IF(ISNUMBER(M39),M39,"")</f>
         <v/>
       </c>
-      <c r="W39" s="38" t="inlineStr">
-        <is>
-          <t>OneWater Marine Inc</t>
-        </is>
-      </c>
-      <c r="X39" t="n">
-        <v>11.8026708373928</v>
-      </c>
-      <c r="Y39" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W39" s="38" t="n"/>
+      <c r="Y39" s="38" t="n"/>
       <c r="Z39">
         <f>IF(AND($W39=$A39,ISNUMBER($X39)),$X39,"")</f>
         <v/>
@@ -10178,44 +8725,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="38" t="inlineStr">
-        <is>
-          <t>American Eagle Outfitters, Inc.</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>17.39</v>
-      </c>
-      <c r="C40" t="n">
-        <v>2914.10026087</v>
-      </c>
-      <c r="D40" s="38" t="n">
-        <v>10.7793487760883</v>
-      </c>
-      <c r="E40" s="38" t="n">
-        <v>4.49318075203224</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.515503446956008</v>
-      </c>
-      <c r="G40" s="38" t="n">
-        <v>36.51045</v>
-      </c>
-      <c r="H40" t="n">
-        <v>3.46088</v>
-      </c>
-      <c r="I40" s="38" t="n">
-        <v>6.4830040757323</v>
-      </c>
-      <c r="J40" t="n">
-        <v>-0.308668650396358</v>
-      </c>
-      <c r="K40" t="n">
-        <v>5652.921</v>
-      </c>
-      <c r="L40" t="n">
-        <v>5015.721</v>
-      </c>
+      <c r="A40" s="38" t="n"/>
+      <c r="D40" s="38" t="n"/>
+      <c r="E40" s="38" t="n"/>
+      <c r="G40" s="38" t="n"/>
+      <c r="I40" s="38" t="n"/>
       <c r="M40" s="84">
         <f>IFERROR(((K40/L40)^(1/3)-1)*100,"")</f>
         <v/>
@@ -10252,17 +8766,8 @@
         <f>IF(ISNUMBER(M40),M40,"")</f>
         <v/>
       </c>
-      <c r="W40" s="38" t="inlineStr">
-        <is>
-          <t>American Eagle Outfitters, Inc.</t>
-        </is>
-      </c>
-      <c r="X40" t="n">
-        <v>9.288415056833561</v>
-      </c>
-      <c r="Y40" s="38" t="n">
-        <v>0.814773250599435</v>
-      </c>
+      <c r="W40" s="38" t="n"/>
+      <c r="Y40" s="38" t="n"/>
       <c r="Z40">
         <f>IF(AND($W40=$A40,ISNUMBER($X40)),$X40,"")</f>
         <v/>
@@ -10273,44 +8778,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="38" t="inlineStr">
-        <is>
-          <t>Barnes &amp; Noble Education Inc</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>12.72</v>
-      </c>
-      <c r="C41" t="n">
-        <v>440.9385456</v>
-      </c>
-      <c r="D41" s="38" t="n">
-        <v>26.5969681129117</v>
-      </c>
-      <c r="E41" s="38" t="n">
-        <v>6.48908493588505</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.257141509123673</v>
-      </c>
-      <c r="G41" t="n">
-        <v>21.35377</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.98392</v>
-      </c>
-      <c r="I41" s="38" t="n">
-        <v>8.00661590827022</v>
-      </c>
-      <c r="J41" s="38" t="n">
-        <v>0.806521038726722</v>
-      </c>
-      <c r="K41" s="38" t="n">
-        <v>1714.77</v>
-      </c>
-      <c r="L41" s="38" t="n">
-        <v>1516.549</v>
-      </c>
+      <c r="A41" s="38" t="n"/>
+      <c r="D41" s="38" t="n"/>
+      <c r="E41" s="38" t="n"/>
+      <c r="I41" s="38" t="n"/>
+      <c r="J41" s="38" t="n"/>
+      <c r="K41" s="38" t="n"/>
+      <c r="L41" s="38" t="n"/>
       <c r="M41" s="84">
         <f>IFERROR(((K41/L41)^(1/3)-1)*100,"")</f>
         <v/>
@@ -10347,21 +8821,9 @@
         <f>IF(ISNUMBER(M41),M41,"")</f>
         <v/>
       </c>
-      <c r="W41" s="38" t="inlineStr">
-        <is>
-          <t>Barnes &amp; Noble Education Inc</t>
-        </is>
-      </c>
-      <c r="X41" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="Y41" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W41" s="38" t="n"/>
+      <c r="X41" s="38" t="n"/>
+      <c r="Y41" s="38" t="n"/>
       <c r="Z41">
         <f>IF(AND($W41=$A41,ISNUMBER($X41)),$X41,"")</f>
         <v/>
@@ -10372,48 +8834,12 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="38" t="inlineStr">
-        <is>
-          <t>1-800-FLOWERS.COM, Inc.</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="C42" t="n">
-        <v>229.47256914</v>
-      </c>
-      <c r="D42" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E42" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>0.154547526423467</v>
-      </c>
-      <c r="G42" t="n">
-        <v>38.69539</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-11.86439</v>
-      </c>
-      <c r="I42" s="38" t="n">
-        <v>-7.00650193626886</v>
-      </c>
-      <c r="J42" s="38" t="n">
-        <v>-18.0479022134126</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1547.015</v>
-      </c>
-      <c r="L42" s="38" t="n">
-        <v>2104.939</v>
-      </c>
+      <c r="A42" s="38" t="n"/>
+      <c r="D42" s="38" t="n"/>
+      <c r="E42" s="38" t="n"/>
+      <c r="I42" s="38" t="n"/>
+      <c r="J42" s="38" t="n"/>
+      <c r="L42" s="38" t="n"/>
       <c r="M42" s="84">
         <f>IFERROR(((K42/L42)^(1/3)-1)*100,"")</f>
         <v/>
@@ -10450,21 +8876,9 @@
         <f>IF(ISNUMBER(M42),M42,"")</f>
         <v/>
       </c>
-      <c r="W42" s="38" t="inlineStr">
-        <is>
-          <t>1-800-FLOWERS.COM, Inc.</t>
-        </is>
-      </c>
-      <c r="X42" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="Y42" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W42" s="38" t="n"/>
+      <c r="X42" s="38" t="n"/>
+      <c r="Y42" s="38" t="n"/>
       <c r="Z42">
         <f>IF(AND($W42=$A42,ISNUMBER($X42)),$X42,"")</f>
         <v/>
@@ -10475,58 +8889,14 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="38" t="inlineStr">
-        <is>
-          <t>Cazoo Group Ltd</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.0004898984</v>
-      </c>
-      <c r="D43" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E43" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F43" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>1.62319</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-41.49653</v>
-      </c>
-      <c r="I43" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="J43" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="K43" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="L43" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="A43" s="38" t="n"/>
+      <c r="D43" s="38" t="n"/>
+      <c r="E43" s="38" t="n"/>
+      <c r="F43" s="38" t="n"/>
+      <c r="I43" s="38" t="n"/>
+      <c r="J43" s="38" t="n"/>
+      <c r="K43" s="38" t="n"/>
+      <c r="L43" s="38" t="n"/>
       <c r="M43" s="84">
         <f>IFERROR(((K43/L43)^(1/3)-1)*100,"")</f>
         <v/>
@@ -10563,21 +8933,9 @@
         <f>IF(ISNUMBER(M43),M43,"")</f>
         <v/>
       </c>
-      <c r="W43" s="38" t="inlineStr">
-        <is>
-          <t>Cazoo Group Ltd</t>
-        </is>
-      </c>
-      <c r="X43" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="Y43" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W43" s="38" t="n"/>
+      <c r="X43" s="38" t="n"/>
+      <c r="Y43" s="38" t="n"/>
       <c r="Z43">
         <f>IF(AND($W43=$A43,ISNUMBER($X43)),$X43,"")</f>
         <v/>
@@ -10588,44 +8946,12 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="38" t="inlineStr">
-        <is>
-          <t>Petco Health and Wellness Company Inc</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C44" t="n">
-        <v>815.976</v>
-      </c>
-      <c r="D44" s="38" t="n">
-        <v>26.2390670553936</v>
-      </c>
-      <c r="E44" s="38" t="n">
-        <v>5.85790811614345</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.14655289899859</v>
-      </c>
-      <c r="G44" t="n">
-        <v>38.66619</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.15208</v>
-      </c>
-      <c r="I44" s="38" t="n">
-        <v>29.1463229310666</v>
-      </c>
-      <c r="J44" s="38" t="n">
-        <v>3.64003506704079</v>
-      </c>
-      <c r="K44" s="38" t="n">
-        <v>5965.491</v>
-      </c>
-      <c r="L44" t="n">
-        <v>6165.821</v>
-      </c>
+      <c r="A44" s="38" t="n"/>
+      <c r="D44" s="38" t="n"/>
+      <c r="E44" s="38" t="n"/>
+      <c r="I44" s="38" t="n"/>
+      <c r="J44" s="38" t="n"/>
+      <c r="K44" s="38" t="n"/>
       <c r="M44" s="84">
         <f>IFERROR(((K44/L44)^(1/3)-1)*100,"")</f>
         <v/>
@@ -10662,17 +8988,8 @@
         <f>IF(ISNUMBER(M44),M44,"")</f>
         <v/>
       </c>
-      <c r="W44" s="38" t="inlineStr">
-        <is>
-          <t>Petco Health and Wellness Company Inc</t>
-        </is>
-      </c>
-      <c r="X44" t="n">
-        <v>10.5132330771465</v>
-      </c>
-      <c r="Y44" s="38" t="n">
-        <v>0.955748461558772</v>
-      </c>
+      <c r="W44" s="38" t="n"/>
+      <c r="Y44" s="38" t="n"/>
       <c r="Z44">
         <f>IF(AND($W44=$A44,ISNUMBER($X44)),$X44,"")</f>
         <v/>
@@ -10683,44 +9000,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="38" t="inlineStr">
-        <is>
-          <t>Arhaus, Inc.</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="C45" t="n">
-        <v>1190.7145572</v>
-      </c>
-      <c r="D45" s="38" t="n">
-        <v>17.8904440846773</v>
-      </c>
-      <c r="E45" s="38" t="n">
-        <v>7.04824321447873</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.878534127147187</v>
-      </c>
-      <c r="G45" t="n">
-        <v>38.89207</v>
-      </c>
-      <c r="H45" t="n">
-        <v>4.87637</v>
-      </c>
-      <c r="I45" s="38" t="n">
-        <v>3.43180485641248</v>
-      </c>
-      <c r="J45" s="38" t="n">
-        <v>-1.38662158229515</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1408.588</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1293.83</v>
-      </c>
+      <c r="A45" s="38" t="n"/>
+      <c r="D45" s="38" t="n"/>
+      <c r="E45" s="38" t="n"/>
+      <c r="I45" s="38" t="n"/>
+      <c r="J45" s="38" t="n"/>
       <c r="M45" s="84">
         <f>IFERROR(((K45/L45)^(1/3)-1)*100,"")</f>
         <v/>
@@ -10757,17 +9041,8 @@
         <f>IF(ISNUMBER(M45),M45,"")</f>
         <v/>
       </c>
-      <c r="W45" s="38" t="inlineStr">
-        <is>
-          <t>Arhaus, Inc.</t>
-        </is>
-      </c>
-      <c r="X45" t="n">
-        <v>15.6779138577644</v>
-      </c>
-      <c r="Y45" s="38" t="n">
-        <v>2.6572735352143</v>
-      </c>
+      <c r="W45" s="38" t="n"/>
+      <c r="Y45" s="38" t="n"/>
       <c r="Z45">
         <f>IF(AND($W45=$A45,ISNUMBER($X45)),$X45,"")</f>
         <v/>
@@ -10778,46 +9053,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="38" t="inlineStr">
-        <is>
-          <t>Sleep Number Corp</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0.0161</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.5186025</v>
-      </c>
-      <c r="D46" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>10.0671761988012</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.000277516871377</v>
-      </c>
-      <c r="G46" s="38" t="n">
-        <v>59.69152</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-9.34911</v>
-      </c>
-      <c r="I46" s="38" t="n">
-        <v>-4561.68259890764</v>
-      </c>
-      <c r="J46" s="38" t="n">
-        <v>9.765351315351319</v>
-      </c>
-      <c r="K46" s="38" t="n">
-        <v>1337.176</v>
-      </c>
-      <c r="L46" s="38" t="n">
-        <v>2113.694</v>
-      </c>
+      <c r="A46" s="38" t="n"/>
+      <c r="D46" s="38" t="n"/>
+      <c r="G46" s="38" t="n"/>
+      <c r="I46" s="38" t="n"/>
+      <c r="J46" s="38" t="n"/>
+      <c r="K46" s="38" t="n"/>
+      <c r="L46" s="38" t="n"/>
       <c r="M46" s="84">
         <f>IFERROR(((K46/L46)^(1/3)-1)*100,"")</f>
         <v/>
@@ -10854,21 +9096,9 @@
         <f>IF(ISNUMBER(M46),M46,"")</f>
         <v/>
       </c>
-      <c r="W46" s="38" t="inlineStr">
-        <is>
-          <t>Sleep Number Corp</t>
-        </is>
-      </c>
-      <c r="X46" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="Y46" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W46" s="38" t="n"/>
+      <c r="X46" s="38" t="n"/>
+      <c r="Y46" s="38" t="n"/>
       <c r="Z46">
         <f>IF(AND($W46=$A46,ISNUMBER($X46)),$X46,"")</f>
         <v/>
@@ -10879,46 +9109,12 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="38" t="inlineStr">
-        <is>
-          <t>Stitch Fix, Inc.</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="C47" t="n">
-        <v>409.61737792</v>
-      </c>
-      <c r="D47" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E47" s="38" t="n">
-        <v>99.1559314285718</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.304847048529958</v>
-      </c>
-      <c r="G47" t="n">
-        <v>44.42486</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-2.27625</v>
-      </c>
-      <c r="I47" t="n">
-        <v>4.44829760214876</v>
-      </c>
-      <c r="J47" s="38" t="n">
-        <v>-104.518469069871</v>
-      </c>
-      <c r="K47" s="38" t="n">
-        <v>1334.928</v>
-      </c>
-      <c r="L47" s="38" t="n">
-        <v>1654.677</v>
-      </c>
+      <c r="A47" s="38" t="n"/>
+      <c r="D47" s="38" t="n"/>
+      <c r="E47" s="38" t="n"/>
+      <c r="J47" s="38" t="n"/>
+      <c r="K47" s="38" t="n"/>
+      <c r="L47" s="38" t="n"/>
       <c r="M47" s="84">
         <f>IFERROR(((K47/L47)^(1/3)-1)*100,"")</f>
         <v/>
@@ -10955,21 +9151,9 @@
         <f>IF(ISNUMBER(M47),M47,"")</f>
         <v/>
       </c>
-      <c r="W47" s="38" t="inlineStr">
-        <is>
-          <t>Stitch Fix, Inc.</t>
-        </is>
-      </c>
-      <c r="X47" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="Y47" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W47" s="38" t="n"/>
+      <c r="X47" s="38" t="n"/>
+      <c r="Y47" s="38" t="n"/>
       <c r="Z47">
         <f>IF(AND($W47=$A47,ISNUMBER($X47)),$X47,"")</f>
         <v/>
@@ -10980,44 +9164,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="38" t="inlineStr">
-        <is>
-          <t>Academy Sports and Outdoors, Inc.</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>44.94</v>
-      </c>
-      <c r="C48" t="n">
-        <v>2708.96244528</v>
-      </c>
-      <c r="D48" s="38" t="n">
-        <v>7.91803581968585</v>
-      </c>
-      <c r="E48" t="n">
-        <v>4.45229385466774</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.453629803071578</v>
-      </c>
-      <c r="G48" t="n">
-        <v>34.78389</v>
-      </c>
-      <c r="H48" t="n">
-        <v>6.22406</v>
-      </c>
-      <c r="I48" t="n">
-        <v>8.73013209954469</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.239381149356443</v>
-      </c>
-      <c r="K48" t="n">
-        <v>6144.009</v>
-      </c>
-      <c r="L48" t="n">
-        <v>6310.952</v>
-      </c>
+      <c r="A48" s="38" t="n"/>
+      <c r="D48" s="38" t="n"/>
       <c r="M48" s="84">
         <f>IFERROR(((K48/L48)^(1/3)-1)*100,"")</f>
         <v/>
@@ -11054,17 +9202,8 @@
         <f>IF(ISNUMBER(M48),M48,"")</f>
         <v/>
       </c>
-      <c r="W48" s="38" t="inlineStr">
-        <is>
-          <t>Academy Sports and Outdoors, Inc.</t>
-        </is>
-      </c>
-      <c r="X48" t="n">
-        <v>6.6703286688335</v>
-      </c>
-      <c r="Y48" s="38" t="n">
-        <v>0.825195639523996</v>
-      </c>
+      <c r="W48" s="38" t="n"/>
+      <c r="Y48" s="38" t="n"/>
       <c r="Z48">
         <f>IF(AND($W48=$A48,ISNUMBER($X48)),$X48,"")</f>
         <v/>
@@ -11075,46 +9214,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="38" t="inlineStr">
-        <is>
-          <t>The Buckle, Inc.</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>43.15</v>
-      </c>
-      <c r="C49" t="n">
-        <v>2222.9152274</v>
-      </c>
-      <c r="D49" s="38" t="n">
-        <v>9.94720947924111</v>
-      </c>
-      <c r="E49" s="38" t="n">
-        <v>6.52419515741437</v>
-      </c>
-      <c r="F49" t="n">
-        <v>1.67321669351342</v>
-      </c>
-      <c r="G49" t="n">
-        <v>48.99375</v>
-      </c>
-      <c r="H49" t="n">
-        <v>16.16107</v>
-      </c>
-      <c r="I49" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="J49" s="38" t="n">
-        <v>-0.924024523004641</v>
-      </c>
-      <c r="K49" t="n">
-        <v>1328.528</v>
-      </c>
-      <c r="L49" t="n">
-        <v>1309.409</v>
-      </c>
+      <c r="A49" s="38" t="n"/>
+      <c r="D49" s="38" t="n"/>
+      <c r="E49" s="38" t="n"/>
+      <c r="I49" s="38" t="n"/>
+      <c r="J49" s="38" t="n"/>
       <c r="M49" s="84">
         <f>IFERROR(((K49/L49)^(1/3)-1)*100,"")</f>
         <v/>
@@ -11151,19 +9255,8 @@
         <f>IF(ISNUMBER(M49),M49,"")</f>
         <v/>
       </c>
-      <c r="W49" s="38" t="inlineStr">
-        <is>
-          <t>The Buckle, Inc.</t>
-        </is>
-      </c>
-      <c r="X49" t="n">
-        <v>10.3088448694444</v>
-      </c>
-      <c r="Y49" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W49" s="38" t="n"/>
+      <c r="Y49" s="38" t="n"/>
       <c r="Z49">
         <f>IF(AND($W49=$A49,ISNUMBER($X49)),$X49,"")</f>
         <v/>
@@ -11174,48 +9267,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="38" t="inlineStr">
-        <is>
-          <t>Lands' End, Inc.</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>10.94</v>
-      </c>
-      <c r="C50" t="n">
-        <v>336.30508498</v>
-      </c>
-      <c r="D50" s="38" t="n">
-        <v>0.9956914048350189</v>
-      </c>
-      <c r="E50" t="n">
-        <v>4.04525301735113</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.256163354782786</v>
-      </c>
-      <c r="G50" t="n">
-        <v>48.69655</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.41254</v>
-      </c>
-      <c r="I50" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="J50" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>1320.813</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1533.507</v>
-      </c>
+      <c r="A50" s="38" t="n"/>
+      <c r="D50" s="38" t="n"/>
+      <c r="I50" s="38" t="n"/>
+      <c r="J50" s="38" t="n"/>
       <c r="M50" s="84">
         <f>IFERROR(((K50/L50)^(1/3)-1)*100,"")</f>
         <v/>
@@ -11252,19 +9307,8 @@
         <f>IF(ISNUMBER(M50),M50,"")</f>
         <v/>
       </c>
-      <c r="W50" s="38" t="inlineStr">
-        <is>
-          <t>Lands' End, Inc.</t>
-        </is>
-      </c>
-      <c r="X50" t="n">
-        <v>14.4908985374654</v>
-      </c>
-      <c r="Y50" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W50" s="38" t="n"/>
+      <c r="Y50" s="38" t="n"/>
       <c r="Z50">
         <f>IF(AND($W50=$A50,ISNUMBER($X50)),$X50,"")</f>
         <v/>
@@ -11275,44 +9319,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="38" t="inlineStr">
-        <is>
-          <t>Revolve Group, Inc.</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="C51" t="n">
-        <v>1517.673717</v>
-      </c>
-      <c r="D51" s="38" t="n">
-        <v>21.1944328627871</v>
-      </c>
-      <c r="E51" s="38" t="n">
-        <v>13.44635939101</v>
-      </c>
-      <c r="F51" t="n">
-        <v>1.15827579530286</v>
-      </c>
-      <c r="G51" t="n">
-        <v>53.5036</v>
-      </c>
-      <c r="H51" t="n">
-        <v>5.03467</v>
-      </c>
-      <c r="I51" s="38" t="n">
-        <v>1.66247300526267</v>
-      </c>
-      <c r="J51" t="n">
-        <v>-3.25495611885775</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1310.287</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1081.202</v>
-      </c>
+      <c r="A51" s="38" t="n"/>
+      <c r="D51" s="38" t="n"/>
+      <c r="E51" s="38" t="n"/>
+      <c r="I51" s="38" t="n"/>
       <c r="M51" s="84">
         <f>IFERROR(((K51/L51)^(1/3)-1)*100,"")</f>
         <v/>
@@ -11349,17 +9359,7 @@
         <f>IF(ISNUMBER(M51),M51,"")</f>
         <v/>
       </c>
-      <c r="W51" s="38" t="inlineStr">
-        <is>
-          <t>Revolve Group, Inc.</t>
-        </is>
-      </c>
-      <c r="X51" t="n">
-        <v>20.7470751928937</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>2.09566416089835</v>
-      </c>
+      <c r="W51" s="38" t="n"/>
       <c r="Z51">
         <f>IF(AND($W51=$A51,ISNUMBER($X51)),$X51,"")</f>
         <v/>
@@ -11370,48 +9370,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="38" t="inlineStr">
-        <is>
-          <t>America's CAR-MART Inc</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C52" t="n">
-        <v>19.14631953</v>
-      </c>
-      <c r="D52" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E52" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>0.016229822920846</v>
-      </c>
-      <c r="G52" s="38" t="n">
-        <v>48.18728</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-10.85843</v>
-      </c>
-      <c r="I52" s="38" t="n">
-        <v>329.823180382282</v>
-      </c>
-      <c r="J52" t="n">
-        <v>-58.2927123760241</v>
-      </c>
-      <c r="K52" t="n">
-        <v>1281.122</v>
-      </c>
-      <c r="L52" t="n">
-        <v>1400.412</v>
-      </c>
+      <c r="A52" s="38" t="n"/>
+      <c r="D52" s="38" t="n"/>
+      <c r="E52" s="38" t="n"/>
+      <c r="G52" s="38" t="n"/>
+      <c r="I52" s="38" t="n"/>
       <c r="M52" s="84">
         <f>IFERROR(((K52/L52)^(1/3)-1)*100,"")</f>
         <v/>
@@ -11448,21 +9411,9 @@
         <f>IF(ISNUMBER(M52),M52,"")</f>
         <v/>
       </c>
-      <c r="W52" s="38" t="inlineStr">
-        <is>
-          <t>America's CAR-MART Inc</t>
-        </is>
-      </c>
-      <c r="X52" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="Y52" s="38" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="W52" s="38" t="n"/>
+      <c r="X52" s="38" t="n"/>
+      <c r="Y52" s="38" t="n"/>
       <c r="Z52">
         <f>IF(AND($W52=$A52,ISNUMBER($X52)),$X52,"")</f>
         <v/>
@@ -12271,22 +10222,10 @@
       <c r="E6" s="92" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="58">
-        <f>_xll.ciqfunctions.udf.CIQ("GME", "IQ_NEWS", 1)</f>
-        <v/>
-      </c>
-      <c r="B7" s="59">
-        <f>_xll.ciqfunctions.udf.CIQ("GME", "IQ_NEWS", 1)</f>
-        <v/>
-      </c>
-      <c r="C7" s="59">
-        <f>_xll.ciqfunctions.udf.CIQ("GME", "IQ_NEWS", 1)</f>
-        <v/>
-      </c>
-      <c r="D7" s="55">
-        <f>_xll.ciqfunctions.udf.CIQ("GME", "IQ_NEWS", 1)</f>
-        <v/>
-      </c>
+      <c r="A7" s="58" t="n"/>
+      <c r="B7" s="59" t="n"/>
+      <c r="C7" s="59" t="n"/>
+      <c r="D7" s="55" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="58" t="n"/>
@@ -12490,7 +10429,7 @@
     <row r="2">
       <c r="A2" s="89" t="inlineStr">
         <is>
-          <t>Auto from the other sheets. Flags are rough heuristics.</t>
+          <t>Auto from the other sheets. Flags are rough heuristics, and blank when the figure behind them is.</t>
         </is>
       </c>
     </row>
@@ -12703,7 +10642,7 @@
         </is>
       </c>
       <c r="B23" s="32">
-        <f>IFERROR(IF(History!H11&gt;0,"yes","no"),"")</f>
+        <f>IF(ISNUMBER(History!H11),IF(History!H11&gt;0,"yes","no"),"")</f>
         <v/>
       </c>
     </row>
@@ -12714,7 +10653,7 @@
         </is>
       </c>
       <c r="B24" s="32">
-        <f>IFERROR(IF(History!H15&gt;0,"yes","no"),"")</f>
+        <f>IF(ISNUMBER(History!H15),IF(History!H15&gt;0,"yes","no"),"")</f>
         <v/>
       </c>
     </row>
@@ -12725,7 +10664,7 @@
         </is>
       </c>
       <c r="B25" s="32">
-        <f>IFERROR(IF(History!I5&gt;0,"yes","no"),"")</f>
+        <f>IF(ISNUMBER(History!I5),IF(History!I5&gt;0,"yes","no"),"")</f>
         <v/>
       </c>
     </row>
@@ -12736,7 +10675,7 @@
         </is>
       </c>
       <c r="B26" s="32">
-        <f>IFERROR(IF(History!I33&gt;1,"yes","no"),"")</f>
+        <f>IF(ISNUMBER(History!I33),IF(History!I33&gt;1,"yes","no"),"")</f>
         <v/>
       </c>
     </row>
@@ -12747,7 +10686,7 @@
         </is>
       </c>
       <c r="B27" s="32">
-        <f>IFERROR(IF(Snapshot!D42&gt;3,"yes","no"),"")</f>
+        <f>IF(ISNUMBER(Snapshot!D42),IF(Snapshot!D42&gt;3,"yes","no"),IF(AND(ISNUMBER(History!H10),N(History!H10)&lt;=0,N(Snapshot!D41)&gt;0),"yes",""))</f>
         <v/>
       </c>
     </row>
